--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95.949</v>
+        <v>87.697</v>
       </c>
       <c r="E4" t="n">
         <v>37.14</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3871</v>
+        <v>0.4235</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1219</v>
+        <v>0.1334</v>
       </c>
       <c r="H4" t="n">
         <v>0.11</v>
@@ -656,16 +656,16 @@
         <v>0.01</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1191</v>
+        <v>1.2338</v>
       </c>
       <c r="K4" t="n">
-        <v>107.38</v>
+        <v>108.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0487</v>
+        <v>0.0524</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0732</v>
+        <v>0.081</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.481</v>
+        <v>10.137</v>
       </c>
       <c r="E6" t="n">
         <v>6.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.674</v>
+        <v>0.6304</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0881</v>
+        <v>0.0824</v>
       </c>
       <c r="H6" t="n">
         <v>0.11</v>
@@ -762,16 +762,16 @@
         <v>0.01</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7237</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>7.34</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0774</v>
+        <v>0.073</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0107</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.335</v>
+        <v>26.91</v>
       </c>
       <c r="E7" t="n">
         <v>27.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9951</v>
+        <v>1.0108</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1143</v>
+        <v>0.1161</v>
       </c>
       <c r="H7" t="n">
         <v>0.11</v>
@@ -815,16 +815,16 @@
         <v>0.01</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0431</v>
+        <v>1.0612</v>
       </c>
       <c r="K7" t="n">
-        <v>28.51</v>
+        <v>28.56</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1095</v>
+        <v>0.1111</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0048</v>
+        <v>0.005</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.477</v>
+        <v>24.64</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.974</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1083</v>
+        <v>0.112</v>
       </c>
       <c r="H8" t="n">
         <v>0.11</v>
@@ -868,16 +868,16 @@
         <v>0.01</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9828</v>
+        <v>1.0196</v>
       </c>
       <c r="K8" t="n">
-        <v>25.04</v>
+        <v>25.12</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1042</v>
+        <v>0.1074</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0041</v>
+        <v>0.0046</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32.116</v>
+        <v>31.33</v>
       </c>
       <c r="E9" t="n">
         <v>17.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5371</v>
+        <v>0.5506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="H9" t="n">
         <v>0.11</v>
@@ -921,16 +921,16 @@
         <v>0.01</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5556</v>
+        <v>0.572</v>
       </c>
       <c r="K9" t="n">
-        <v>17.84</v>
+        <v>17.92</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.318</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>70.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8498</v>
+        <v>0.9134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.082</v>
+        <v>0.0882</v>
       </c>
       <c r="H10" t="n">
         <v>0.11</v>
@@ -974,16 +974,16 @@
         <v>0.01</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>60.01</v>
+        <v>60.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.095</v>
+        <v>0.1013</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0129</v>
+        <v>-0.0132</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.337</v>
+        <v>5.218</v>
       </c>
       <c r="E11" t="n">
         <v>7.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4428</v>
+        <v>1.4758</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1388</v>
+        <v>0.142</v>
       </c>
       <c r="H11" t="n">
         <v>0.11</v>
@@ -1027,16 +1027,16 @@
         <v>0.01</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2883</v>
+        <v>1.3201</v>
       </c>
       <c r="K11" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1543</v>
+        <v>0.1576</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0154</v>
+        <v>-0.0156</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1062,16 +1062,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.241</v>
+        <v>15.269</v>
       </c>
       <c r="E12" t="n">
         <v>14.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9776</v>
+        <v>0.9758</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="H12" t="n">
         <v>0.11</v>
@@ -1080,16 +1080,16 @@
         <v>0.01</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6528</v>
+        <v>0.6514</v>
       </c>
       <c r="K12" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1078</v>
+        <v>0.1076</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0325</v>
+        <v>-0.0324</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.736</v>
+        <v>25.435</v>
       </c>
       <c r="E13" t="n">
         <v>28.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0548</v>
+        <v>1.1087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="H13" t="n">
         <v>0.11</v>
@@ -1133,16 +1133,16 @@
         <v>0.01</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7214</v>
+        <v>0.7634</v>
       </c>
       <c r="K13" t="n">
-        <v>19.29</v>
+        <v>19.42</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1155</v>
+        <v>0.1209</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0333</v>
+        <v>-0.0345</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.289</v>
+        <v>13.095</v>
       </c>
       <c r="E14" t="n">
         <v>16.4</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0727</v>
+        <v>1.2524</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0788</v>
+        <v>0.092</v>
       </c>
       <c r="H14" t="n">
         <v>0.11</v>
@@ -1186,16 +1186,16 @@
         <v>0.01</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6883</v>
+        <v>0.8204</v>
       </c>
       <c r="K14" t="n">
-        <v>10.52</v>
+        <v>10.74</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1173</v>
+        <v>0.1352</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0384</v>
+        <v>-0.0432</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1217,20 +1217,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.471</v>
+        <v>80.35299999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>34.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2118</v>
+        <v>0.9408</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0487</v>
       </c>
       <c r="H15" t="n">
         <v>0.11</v>
@@ -1239,16 +1239,16 @@
         <v>0.01</v>
       </c>
       <c r="J15" t="n">
-        <v>0.717</v>
+        <v>0.3872</v>
       </c>
       <c r="K15" t="n">
-        <v>20.41</v>
+        <v>31.11</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1312</v>
+        <v>0.1041</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0495</v>
+        <v>-0.0554</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1270,20 +1270,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>83.869</v>
+        <v>24.219</v>
       </c>
       <c r="E16" t="n">
-        <v>75.59999999999999</v>
+        <v>34.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9014</v>
+        <v>1.4245</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0467</v>
+        <v>0.096</v>
       </c>
       <c r="H16" t="n">
         <v>0.11</v>
@@ -1292,16 +1292,16 @@
         <v>0.01</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3668</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>30.76</v>
+        <v>20.84</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1001</v>
+        <v>0.1524</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0535</v>
+        <v>-0.0564</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1327,16 +1327,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57.908</v>
+        <v>52.589</v>
       </c>
       <c r="E17" t="n">
         <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>1.347</v>
+        <v>1.4832</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0897</v>
+        <v>0.0988</v>
       </c>
       <c r="H17" t="n">
         <v>0.11</v>
@@ -1345,16 +1345,16 @@
         <v>0.01</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7971</v>
+        <v>0.8878</v>
       </c>
       <c r="K17" t="n">
-        <v>46.16</v>
+        <v>46.69</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1447</v>
+        <v>0.1583</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.055</v>
+        <v>-0.0595</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.96</v>
+        <v>15.935</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0025</v>
+        <v>1.0041</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0477</v>
+        <v>0.0478</v>
       </c>
       <c r="H18" t="n">
         <v>0.11</v>
@@ -1398,16 +1398,16 @@
         <v>0.01</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3774</v>
+        <v>0.3781</v>
       </c>
       <c r="K18" t="n">
-        <v>6.02</v>
+        <v>6.03</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1103</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0625</v>
+        <v>-0.0626</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.934</v>
+        <v>33.881</v>
       </c>
       <c r="E19" t="n">
         <v>47.7</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1945</v>
+        <v>1.4079</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0551</v>
+        <v>0.0649</v>
       </c>
       <c r="H19" t="n">
         <v>0.11</v>
@@ -1451,16 +1451,16 @@
         <v>0.01</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4506</v>
+        <v>0.549</v>
       </c>
       <c r="K19" t="n">
-        <v>17.99</v>
+        <v>18.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1294</v>
+        <v>0.1508</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0859</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.632</v>
+        <v>2.073</v>
       </c>
       <c r="E20" t="n">
         <v>5.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9757</v>
+        <v>2.5082</v>
       </c>
       <c r="G20" t="n">
-        <v>0.127</v>
+        <v>0.1613</v>
       </c>
       <c r="H20" t="n">
         <v>0.11</v>
@@ -1504,16 +1504,16 @@
         <v>0.01</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1702</v>
+        <v>1.5126</v>
       </c>
       <c r="K20" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2076</v>
+        <v>0.2608</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0805</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.204</v>
+        <v>15.034</v>
       </c>
       <c r="E21" t="n">
         <v>12.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8024</v>
+        <v>0.8115</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1095</v>
+        <v>0.1107</v>
       </c>
       <c r="H21" t="n">
         <v>0.11</v>
@@ -1557,10 +1557,10 @@
         <v>0.01</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0902</v>
+        <v>0.0912</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0192</v>
+        <v>0.0196</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1802,19 +1802,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0819</v>
+        <v>0.094</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0619</v>
+        <v>0.074</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5624</v>
+        <v>0.6731</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.6404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4652</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="6">
@@ -1824,19 +1824,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0819</v>
+        <v>0.094</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0819</v>
+        <v>0.094</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7442</v>
+        <v>0.8549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7186</v>
+        <v>0.8404</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6874</v>
+        <v>0.8226</v>
       </c>
     </row>
     <row r="7">
@@ -1846,19 +1846,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0819</v>
+        <v>0.094</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1019</v>
+        <v>0.114</v>
       </c>
       <c r="D7" t="n">
-        <v>0.926</v>
+        <v>1.0367</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9186</v>
+        <v>1.0404</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9096</v>
+        <v>1.0449</v>
       </c>
     </row>
     <row r="8">
@@ -1868,19 +1868,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0982</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0772</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7107</v>
+        <v>0.7015</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6817</v>
+        <v>0.6716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6464</v>
+        <v>0.6351</v>
       </c>
     </row>
     <row r="9">
@@ -1890,19 +1890,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0982</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0982</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8925</v>
+        <v>0.8833</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8817</v>
+        <v>0.8716</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8686</v>
+        <v>0.8574000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1912,19 +1912,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0982</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1182</v>
+        <v>0.1172</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0743</v>
+        <v>1.0651</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0817</v>
+        <v>1.0716</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0908</v>
+        <v>1.0796</v>
       </c>
     </row>
     <row r="11">
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0649</v>
+        <v>0.0675</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0449</v>
+        <v>0.0475</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4085</v>
+        <v>0.4321</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3494</v>
+        <v>0.3753</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2771</v>
+        <v>0.3058</v>
       </c>
     </row>
     <row r="15">
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0649</v>
+        <v>0.0675</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0649</v>
+        <v>0.0675</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5903</v>
+        <v>0.6139</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5494</v>
+        <v>0.5753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4993</v>
+        <v>0.5281</v>
       </c>
     </row>
     <row r="16">
@@ -2044,19 +2044,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0649</v>
+        <v>0.0675</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0849</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7722</v>
+        <v>0.7957</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7494</v>
+        <v>0.7753</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7215</v>
+        <v>0.7503</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.137</v>
+        <v>9.821999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>6.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6304</v>
+        <v>0.6506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0824</v>
+        <v>0.0833</v>
       </c>
       <c r="H6" t="n">
         <v>0.11</v>
@@ -762,16 +762,16 @@
         <v>0.01</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7237</v>
+        <v>0.7326</v>
       </c>
       <c r="K6" t="n">
-        <v>7.34</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.073</v>
+        <v>0.0751</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1868,19 +1868,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0772</v>
+        <v>0.0776</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7015</v>
+        <v>0.7055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6716</v>
+        <v>0.6761</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6351</v>
+        <v>0.6401</v>
       </c>
     </row>
     <row r="9">
@@ -1890,19 +1890,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8833</v>
+        <v>0.8874</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8716</v>
+        <v>0.8761</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="10">
@@ -1912,19 +1912,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1172</v>
+        <v>0.1176</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0651</v>
+        <v>1.0692</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0716</v>
+        <v>1.0761</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0796</v>
+        <v>1.0845</v>
       </c>
     </row>
     <row r="11">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -427,15 +427,17 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,45 +473,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ronav_norm</t>
+          <t>r</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>g</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ronav_implied</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>justified_pnav</t>
+          <t>ronav_parity</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>justified_fv</t>
+          <t>justified_pnav_parity</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ronav_implied</t>
+          <t>read_parity</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>ronav_hist</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>justified_pnav_hist</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>read_hist</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -541,143 +553,173 @@
         <v>1.0105</v>
       </c>
       <c r="G2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.2437</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>0.5108</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>5.219</v>
       </c>
-      <c r="K2" t="n">
-        <v>201.38</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3998</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>cheap</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.097</v>
+        <v>87.697</v>
       </c>
       <c r="E3" t="n">
-        <v>21.9</v>
+        <v>37.14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7794</v>
+        <v>0.4235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2751</v>
+        <v>0.11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02</v>
+        <v>0.0524</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8347</v>
+        <v>0.142</v>
       </c>
       <c r="K3" t="n">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0901</v>
+        <v>1.3201</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>0.1334</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.2338</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>cheap</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>87.697</v>
+        <v>9.821999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>37.14</v>
+        <v>6.39</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4235</v>
+        <v>0.6506</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1334</v>
+        <v>0.11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01</v>
+        <v>0.0751</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2338</v>
+        <v>0.1275</v>
       </c>
       <c r="K4" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0524</v>
+        <v>1.1749</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>0.0833</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>cheap</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -687,50 +729,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.453</v>
+        <v>26.91</v>
       </c>
       <c r="E5" t="n">
-        <v>29.7</v>
+        <v>27.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0438</v>
+        <v>1.0108</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1465</v>
+        <v>0.11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02</v>
+        <v>0.1111</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4054</v>
+        <v>0.1421</v>
       </c>
       <c r="K5" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1139</v>
+        <v>1.3211</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>cheap</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>0.1161</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.0612</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>flips (cheap/fair)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -740,50 +792,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.821999999999999</v>
+        <v>2.073</v>
       </c>
       <c r="E6" t="n">
-        <v>6.39</v>
+        <v>5.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6506</v>
+        <v>2.5082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0833</v>
+        <v>0.11</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01</v>
+        <v>0.2608</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7326</v>
+        <v>0.2868</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0751</v>
+        <v>2.7681</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>cheap</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>0.1613</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5126</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>flips (cheap/rich)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -793,50 +855,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.91</v>
+        <v>28.453</v>
       </c>
       <c r="E7" t="n">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0108</v>
+        <v>1.0438</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1161</v>
+        <v>0.11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01</v>
+        <v>0.1139</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0612</v>
+        <v>0.1363</v>
       </c>
       <c r="K7" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.1111</v>
+        <v>1.2924</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0.1465</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.4054</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -850,46 +922,56 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.64</v>
+        <v>31.33</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>17.25</v>
       </c>
       <c r="F8" t="n">
-        <v>0.974</v>
+        <v>0.5506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0196</v>
+        <v>0.0872</v>
       </c>
       <c r="K8" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.1074</v>
+        <v>0.7717000000000001</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>0.0672</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>fair</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>flips (cheap/fair)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -903,46 +985,56 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.33</v>
+        <v>24.64</v>
       </c>
       <c r="E9" t="n">
-        <v>17.25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5506</v>
+        <v>0.974</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0672</v>
+        <v>0.11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01</v>
+        <v>0.1074</v>
       </c>
       <c r="J9" t="n">
-        <v>0.572</v>
+        <v>0.1285</v>
       </c>
       <c r="K9" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.06510000000000001</v>
+        <v>1.1847</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
       </c>
       <c r="M9" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>0.112</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.0196</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>fair</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>flips (cheap/fair)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -952,50 +1044,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77.51000000000001</v>
+        <v>5.218</v>
       </c>
       <c r="E10" t="n">
-        <v>70.8</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134</v>
+        <v>1.4758</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0882</v>
+        <v>0.11</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01</v>
+        <v>0.1576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.1683</v>
       </c>
       <c r="K10" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.1013</v>
+        <v>1.5832</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M10" t="n">
-        <v>-0.0132</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>0.142</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.3201</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1009,51 +1111,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.218</v>
+        <v>25.435</v>
       </c>
       <c r="E11" t="n">
-        <v>7.7</v>
+        <v>28.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4758</v>
+        <v>1.1087</v>
       </c>
       <c r="G11" t="n">
-        <v>0.142</v>
+        <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01</v>
+        <v>0.1209</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3201</v>
+        <v>0.1316</v>
       </c>
       <c r="K11" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1576</v>
+        <v>1.2155</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M11" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="N11" t="inlineStr">
+        <v>0.0863</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1062,46 +1174,56 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.269</v>
+        <v>13.095</v>
       </c>
       <c r="E12" t="n">
-        <v>14.9</v>
+        <v>16.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9758</v>
+        <v>1.2524</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0751</v>
+        <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01</v>
+        <v>0.1352</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6514</v>
+        <v>0.144</v>
       </c>
       <c r="K12" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.1076</v>
+        <v>1.3404</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M12" t="n">
-        <v>-0.0324</v>
-      </c>
-      <c r="N12" t="inlineStr">
+        <v>0.092</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1111,55 +1233,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.435</v>
+        <v>24.219</v>
       </c>
       <c r="E13" t="n">
-        <v>28.2</v>
+        <v>34.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1087</v>
+        <v>1.4245</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0863</v>
+        <v>0.11</v>
       </c>
       <c r="H13" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01</v>
+        <v>0.1524</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7634</v>
+        <v>0.1517</v>
       </c>
       <c r="K13" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1209</v>
+        <v>1.4168</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M13" t="n">
-        <v>-0.0345</v>
-      </c>
-      <c r="N13" t="inlineStr">
+        <v>0.096</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8604000000000001</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1168,46 +1300,56 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.095</v>
+        <v>15.269</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2524</v>
+        <v>0.9758</v>
       </c>
       <c r="G14" t="n">
-        <v>0.092</v>
+        <v>0.11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01</v>
+        <v>0.1076</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8204</v>
+        <v>0.1026</v>
       </c>
       <c r="K14" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.1352</v>
+        <v>0.9265</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M14" t="n">
-        <v>-0.0432</v>
-      </c>
-      <c r="N14" t="inlineStr">
+        <v>0.0751</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1217,50 +1359,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80.35299999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>75.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9408</v>
+        <v>0.9134</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0487</v>
+        <v>0.11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01</v>
+        <v>0.1013</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3872</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1041</v>
+        <v>0.8519</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
       </c>
       <c r="M15" t="n">
-        <v>-0.0554</v>
-      </c>
-      <c r="N15" t="inlineStr">
+        <v>0.0882</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.7818000000000001</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>flips (fair/rich)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1270,45 +1422,55 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24.219</v>
+        <v>15.935</v>
       </c>
       <c r="E16" t="n">
-        <v>34.5</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4245</v>
+        <v>1.0041</v>
       </c>
       <c r="G16" t="n">
-        <v>0.096</v>
+        <v>0.11</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01</v>
+        <v>0.1104</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.0979</v>
       </c>
       <c r="K16" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1524</v>
+        <v>0.8788</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
       </c>
       <c r="M16" t="n">
-        <v>-0.0564</v>
-      </c>
-      <c r="N16" t="inlineStr">
+        <v>0.0478</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1336,37 +1498,47 @@
         <v>1.4832</v>
       </c>
       <c r="G17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.2658</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>0.0988</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="N17" t="n">
         <v>0.8878</v>
       </c>
-      <c r="K17" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.1583</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-0.0595</v>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1380,41 +1552,51 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.935</v>
+        <v>80.35299999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0041</v>
+        <v>0.9408</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0478</v>
+        <v>0.11</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01</v>
+        <v>0.1041</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3781</v>
+        <v>0.0809</v>
       </c>
       <c r="K18" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>0.7085</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
       </c>
       <c r="M18" t="n">
-        <v>-0.0626</v>
-      </c>
-      <c r="N18" t="inlineStr">
+        <v>0.0487</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1442,37 +1624,47 @@
         <v>1.4079</v>
       </c>
       <c r="G19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.0863</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>0.0649</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="N19" t="n">
         <v>0.549</v>
       </c>
-      <c r="K19" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.1508</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-0.0859</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1482,45 +1674,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.073</v>
+        <v>28.097</v>
       </c>
       <c r="E20" t="n">
-        <v>5.2</v>
+        <v>21.9</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5082</v>
+        <v>0.7794</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1613</v>
+        <v>0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.5126</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.2608</v>
+        <v>0.0901</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
       </c>
       <c r="M20" t="n">
-        <v>-0.09959999999999999</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>rich</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>0.2751</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.8347</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1548,26 +1748,36 @@
         <v>0.8115</v>
       </c>
       <c r="G21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>newbuild-heavy (unreliable)</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>0.1107</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
@@ -1599,26 +1809,36 @@
         <v>1.3745</v>
       </c>
       <c r="G22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>newbuild-heavy (unreliable)</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>0.5</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.1456</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.3544</v>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
@@ -1650,26 +1870,36 @@
         <v>0.5744</v>
       </c>
       <c r="G23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>newbuild-heavy (unreliable)</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
         <v>0.209</v>
       </c>
-      <c r="H23" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.0674</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.1416</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>newbuild-heavy (unreliable)</t>
         </is>
@@ -1736,19 +1966,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5108</v>
+        <v>0.2281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4908</v>
+        <v>0.2081</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4618</v>
+        <v>1.8923</v>
       </c>
       <c r="E2" t="n">
-        <v>4.808</v>
+        <v>1.9815</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2311</v>
+        <v>2.0906</v>
       </c>
     </row>
     <row r="3">
@@ -1758,19 +1988,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5108</v>
+        <v>0.2281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5108</v>
+        <v>0.2281</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6437</v>
+        <v>2.0741</v>
       </c>
       <c r="E3" t="n">
-        <v>5.008</v>
+        <v>2.1815</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4534</v>
+        <v>2.3128</v>
       </c>
     </row>
     <row r="4">
@@ -1780,19 +2010,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5108</v>
+        <v>0.2281</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5308</v>
+        <v>0.2481</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8255</v>
+        <v>2.2559</v>
       </c>
       <c r="E4" t="n">
-        <v>5.208</v>
+        <v>2.3815</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6756</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="5">
@@ -1802,19 +2032,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.094</v>
+        <v>0.1393</v>
       </c>
       <c r="C5" t="n">
-        <v>0.074</v>
+        <v>0.1193</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6731</v>
+        <v>1.0845</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6404</v>
+        <v>1.093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6004</v>
+        <v>1.1033</v>
       </c>
     </row>
     <row r="6">
@@ -1824,19 +2054,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.094</v>
+        <v>0.1393</v>
       </c>
       <c r="C6" t="n">
-        <v>0.094</v>
+        <v>0.1393</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8549</v>
+        <v>1.2663</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8404</v>
+        <v>1.293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8226</v>
+        <v>1.3255</v>
       </c>
     </row>
     <row r="7">
@@ -1846,19 +2076,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.094</v>
+        <v>0.1393</v>
       </c>
       <c r="C7" t="n">
-        <v>0.114</v>
+        <v>0.1593</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0367</v>
+        <v>1.4481</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0404</v>
+        <v>1.493</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0449</v>
+        <v>1.5477</v>
       </c>
     </row>
     <row r="8">
@@ -1868,19 +2098,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0776</v>
+        <v>0.108</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7055</v>
+        <v>0.9816</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6761</v>
+        <v>0.9798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6401</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="9">
@@ -1890,19 +2120,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8874</v>
+        <v>1.1634</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8761</v>
+        <v>1.1798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8623</v>
+        <v>1.1997</v>
       </c>
     </row>
     <row r="10">
@@ -1912,19 +2142,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1176</v>
+        <v>0.148</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0692</v>
+        <v>1.3452</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0761</v>
+        <v>1.3798</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0845</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="11">
@@ -1934,19 +2164,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2108</v>
+        <v>0.1363</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1908</v>
+        <v>0.1163</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7346</v>
+        <v>1.0574</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8081</v>
+        <v>1.0632</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8978</v>
+        <v>1.0702</v>
       </c>
     </row>
     <row r="12">
@@ -1956,19 +2186,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2108</v>
+        <v>0.1363</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2108</v>
+        <v>0.1363</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9164</v>
+        <v>1.2393</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0081</v>
+        <v>1.2632</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1201</v>
+        <v>1.2924</v>
       </c>
     </row>
     <row r="13">
@@ -1978,19 +2208,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2108</v>
+        <v>0.1363</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2308</v>
+        <v>0.1563</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0982</v>
+        <v>1.4211</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2081</v>
+        <v>1.4632</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3423</v>
+        <v>1.5146</v>
       </c>
     </row>
     <row r="14">
@@ -2000,19 +2230,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0675</v>
+        <v>0.1147</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0475</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4321</v>
+        <v>0.8611</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3753</v>
+        <v>0.8472</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3058</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="15">
@@ -2022,19 +2252,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0675</v>
+        <v>0.1147</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0675</v>
+        <v>0.1147</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6139</v>
+        <v>1.0429</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5753</v>
+        <v>1.0472</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5281</v>
+        <v>1.0524</v>
       </c>
     </row>
     <row r="16">
@@ -2044,19 +2274,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0675</v>
+        <v>0.1147</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1347</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7957</v>
+        <v>1.2247</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7753</v>
+        <v>1.2472</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7503</v>
+        <v>1.2746</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,32 +540,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>38.586</v>
+        <v>9.821999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>38.99</v>
+        <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0105</v>
+        <v>0.6506</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.111</v>
+        <v>0.0751</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2281</v>
+        <v>0.126</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2437</v>
+        <v>1.1604</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.5108</v>
+        <v>0.0833</v>
       </c>
       <c r="N2" t="n">
-        <v>5.219</v>
+        <v>0.7326</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -593,27 +593,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87.697</v>
+        <v>26.91</v>
       </c>
       <c r="E3" t="n">
-        <v>37.14</v>
+        <v>27.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4235</v>
+        <v>1.0108</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0524</v>
+        <v>0.1111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.142</v>
+        <v>0.1368</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3201</v>
+        <v>1.2682</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1334</v>
+        <v>0.1161</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2338</v>
+        <v>1.0612</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (cheap/fair)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -656,7 +656,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.821999999999999</v>
+        <v>24.64</v>
       </c>
       <c r="E4" t="n">
-        <v>6.39</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6506</v>
+        <v>0.974</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0751</v>
+        <v>0.1074</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1275</v>
+        <v>0.1234</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1749</v>
+        <v>1.1345</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,19 +699,19 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.0833</v>
+        <v>0.112</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7326</v>
+        <v>1.0196</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (cheap/fair)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.91</v>
+        <v>31.33</v>
       </c>
       <c r="E5" t="n">
-        <v>27.2</v>
+        <v>17.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0108</v>
+        <v>0.5506</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1111</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1421</v>
+        <v>0.081</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3211</v>
+        <v>0.7096</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1161</v>
+        <v>0.0672</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0612</v>
+        <v>0.572</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.073</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2</v>
+        <v>70.8</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5082</v>
+        <v>0.9134</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,24 +811,24 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2608</v>
+        <v>0.1013</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2868</v>
+        <v>0.0738</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7681</v>
+        <v>0.6379</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1613</v>
+        <v>0.0882</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5126</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>flips (cheap/rich)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -845,7 +845,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -855,47 +855,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.453</v>
+        <v>13.095</v>
       </c>
       <c r="E7" t="n">
-        <v>29.7</v>
+        <v>16.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0438</v>
+        <v>1.2524</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1139</v>
+        <v>0.1352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1363</v>
+        <v>0.0984</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2924</v>
+        <v>0.8844</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.1465</v>
+        <v>0.092</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4054</v>
+        <v>0.8204</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -918,17 +918,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.33</v>
+        <v>24.219</v>
       </c>
       <c r="E8" t="n">
-        <v>17.25</v>
+        <v>34.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5506</v>
+        <v>1.4245</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,33 +937,33 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.1524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0872</v>
+        <v>0.1051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0672</v>
+        <v>0.096</v>
       </c>
       <c r="N8" t="n">
-        <v>0.572</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>flips (cheap/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -971,7 +971,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dry_bulk</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.64</v>
+        <v>2.073</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.974</v>
+        <v>2.5082</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,33 +1000,33 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1074</v>
+        <v>0.2608</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1285</v>
+        <v>0.212</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1847</v>
+        <v>2.0201</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.112</v>
+        <v>0.1613</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0196</v>
+        <v>1.5126</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>flips (cheap/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.218</v>
+        <v>33.881</v>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>47.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4758</v>
+        <v>1.4079</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,24 +1063,24 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1576</v>
+        <v>0.1508</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1683</v>
+        <v>0.0781</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5832</v>
+        <v>0.6815</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.142</v>
+        <v>0.0649</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3201</v>
+        <v>0.549</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1097,27 +1097,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.435</v>
+        <v>52.589</v>
       </c>
       <c r="E11" t="n">
-        <v>28.2</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1087</v>
+        <v>1.4832</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,24 +1126,18 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1209</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.1316</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.2155</v>
+        <v>0.1583</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.0863</v>
+        <v>0.0988</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7634</v>
+        <v>0.8878</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1152,15 +1146,19 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1170,60 +1168,58 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.095</v>
+        <v>28.453</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4</v>
+        <v>29.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2524</v>
+        <v>1.0438</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1352</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.3404</v>
+        <v>0.1139</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.092</v>
+        <v>0.1465</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8204</v>
+        <v>1.4054</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1233,80 +1229,78 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.219</v>
+        <v>28.097</v>
       </c>
       <c r="E13" t="n">
-        <v>34.5</v>
+        <v>21.9</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4245</v>
+        <v>0.7794</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1524</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.1517</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.4168</v>
+        <v>0.0901</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.096</v>
+        <v>0.2751</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8604000000000001</v>
+        <v>2.8347</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.269</v>
+        <v>80.35299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9758</v>
+        <v>0.9408</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
@@ -1315,24 +1309,18 @@
         <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1076</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.1026</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9265</v>
+        <v>0.1041</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.0751</v>
+        <v>0.0487</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6514</v>
+        <v>0.3872</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1341,15 +1329,19 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1359,17 +1351,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.51000000000001</v>
+        <v>5.218</v>
       </c>
       <c r="E15" t="n">
-        <v>70.8</v>
+        <v>7.7</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9134</v>
+        <v>1.4758</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1378,24 +1370,18 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1013</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.09520000000000001</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.8519</v>
+        <v>0.1576</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.0882</v>
+        <v>0.142</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7818000000000001</v>
+        <v>1.3201</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1404,15 +1390,19 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>flips (fair/rich)</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1426,13 +1416,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.935</v>
+        <v>25.435</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>28.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0041</v>
+        <v>1.1087</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1441,61 +1431,59 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1104</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.0979</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.8788</v>
+        <v>0.1209</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0.0478</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.3781</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>rich</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.589</v>
+        <v>15.935</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4832</v>
+        <v>1.0041</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1504,61 +1492,59 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1583</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1366</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.2658</v>
+        <v>0.1104</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>rich</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0.0988</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.8878</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>rich</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80.35299999999999</v>
+        <v>87.697</v>
       </c>
       <c r="E18" t="n">
-        <v>75.59999999999999</v>
+        <v>37.14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9408</v>
+        <v>0.4235</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1567,41 +1553,39 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1041</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.0809</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.7085</v>
+        <v>0.0524</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.0487</v>
+        <v>0.1334</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3872</v>
+        <v>1.2338</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1615,13 +1599,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33.881</v>
+        <v>15.034</v>
       </c>
       <c r="E19" t="n">
-        <v>47.7</v>
+        <v>12.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4079</v>
+        <v>0.8115</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1630,41 +1614,39 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1508</v>
+        <v>0.0912</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1186</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.0863</v>
+        <v>0.1139</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.549</v>
+        <v>0.1107</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>robust</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>newbuild-heavy (unreliable)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,26 +1656,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.097</v>
+        <v>2.023</v>
       </c>
       <c r="E20" t="n">
-        <v>21.9</v>
+        <v>2.78</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7794</v>
+        <v>1.3745</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0901</v>
+        <v>0.1456</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1701,14 +1683,11 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.2751</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.8347</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1725,7 +1704,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1735,41 +1714,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.034</v>
+        <v>38.586</v>
       </c>
       <c r="E21" t="n">
-        <v>12.2</v>
+        <v>38.99</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8115</v>
+        <v>1.0105</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1555</v>
+        <v>0.111</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.1107</v>
+        <v>0.5108</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.219</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1779,14 +1758,14 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1796,29 +1775,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.023</v>
+        <v>9.401</v>
       </c>
       <c r="E22" t="n">
-        <v>2.78</v>
+        <v>5.4</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3745</v>
+        <v>0.5744</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
       </c>
       <c r="H22" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1456</v>
+        <v>0.0674</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1994</v>
+        <v>0.2217</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1826,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.5</v>
+        <v>0.209</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1847,12 +1826,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1861,13 +1840,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.401</v>
+        <v>15.269</v>
       </c>
       <c r="E23" t="n">
-        <v>5.4</v>
+        <v>14.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5744</v>
+        <v>0.9758</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1876,22 +1855,22 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0674</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.3119</v>
+        <v>0.1076</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.209</v>
+        <v>0.0751</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.6514</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1901,7 +1880,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
     </row>
@@ -1916,10 +1895,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1962,331 +1941,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2281</v>
+        <v>0.0984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2081</v>
+        <v>0.0784</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8923</v>
+        <v>0.7131</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9815</v>
+        <v>0.6844</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0906</v>
+        <v>0.6494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2281</v>
+        <v>0.0984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2281</v>
+        <v>0.0984</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0741</v>
+        <v>0.8949</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1815</v>
+        <v>0.8844</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3128</v>
+        <v>0.8716</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2281</v>
+        <v>0.0984</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2481</v>
+        <v>0.1184</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2559</v>
+        <v>1.0768</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3815</v>
+        <v>1.0844</v>
       </c>
       <c r="F4" t="n">
-        <v>2.535</v>
+        <v>1.0938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1393</v>
+        <v>0.1247</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1193</v>
+        <v>0.1047</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0845</v>
+        <v>0.9522</v>
       </c>
       <c r="E5" t="n">
-        <v>1.093</v>
+        <v>0.9475</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1033</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1393</v>
+        <v>0.1247</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1393</v>
+        <v>0.1247</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2663</v>
+        <v>1.1341</v>
       </c>
       <c r="E6" t="n">
-        <v>1.293</v>
+        <v>1.1475</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3255</v>
+        <v>1.1638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1393</v>
+        <v>0.1247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1593</v>
+        <v>0.1447</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4481</v>
+        <v>1.3159</v>
       </c>
       <c r="E7" t="n">
-        <v>1.493</v>
+        <v>1.3475</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5477</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dry_bulk</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.9816</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9775</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>dry_bulk</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.1634</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.1798</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.1997</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>dry_bulk</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.3452</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.3798</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.422</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>lng</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.1363</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1163</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.0574</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.0632</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.0702</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>lng</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1363</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1363</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.2393</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.2632</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.2924</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>lng</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.1363</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.1563</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.4211</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.4632</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.5146</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8611</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.8472</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8302</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.0429</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.0472</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.0524</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.1147</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.1347</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.2247</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.2472</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.2746</v>
+        <v>1.3861</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.821999999999999</v>
+        <v>10.309</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6506</v>
+        <v>0.6199</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0751</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.126</v>
+        <v>0.1201</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1604</v>
+        <v>1.1009</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0833</v>
+        <v>0.0793</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7326</v>
+        <v>0.6933</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.64</v>
+        <v>24.689</v>
       </c>
       <c r="E4" t="n">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>0.974</v>
+        <v>0.9721</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1074</v>
+        <v>0.1072</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1234</v>
+        <v>0.1232</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1345</v>
+        <v>1.1321</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0196</v>
+        <v>1.0174</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.095</v>
+        <v>12.508</v>
       </c>
       <c r="E7" t="n">
         <v>16.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2524</v>
+        <v>1.3111</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1352</v>
+        <v>0.1411</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8844</v>
+        <v>0.9306</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.092</v>
+        <v>0.0964</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8204</v>
+        <v>0.8636</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.219</v>
+        <v>2.073</v>
       </c>
       <c r="E8" t="n">
-        <v>34.5</v>
+        <v>5.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4245</v>
+        <v>2.5082</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1524</v>
+        <v>0.2608</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1051</v>
+        <v>0.212</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9510999999999999</v>
+        <v>2.0201</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.096</v>
+        <v>0.1613</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8604000000000001</v>
+        <v>1.5126</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.073</v>
+        <v>22.667</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2</v>
+        <v>34.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5082</v>
+        <v>1.522</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2608</v>
+        <v>0.1622</v>
       </c>
       <c r="J9" t="n">
-        <v>0.212</v>
+        <v>0.1123</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0201</v>
+        <v>1.0231</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.1613</v>
+        <v>0.1026</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5126</v>
+        <v>0.9262</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33.881</v>
+        <v>32.16</v>
       </c>
       <c r="E10" t="n">
         <v>47.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4079</v>
+        <v>1.4832</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1508</v>
+        <v>0.1583</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0781</v>
+        <v>0.0823</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6815</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0649</v>
+        <v>0.0684</v>
       </c>
       <c r="N10" t="n">
-        <v>0.549</v>
+        <v>0.5837</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>87.697</v>
+        <v>86.95399999999999</v>
       </c>
       <c r="E18" t="n">
         <v>37.14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4235</v>
+        <v>0.4271</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1553,7 +1553,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0524</v>
+        <v>0.0527</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.1334</v>
+        <v>0.1345</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2338</v>
+        <v>1.2452</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.034</v>
+        <v>11.581</v>
       </c>
       <c r="E19" t="n">
         <v>12.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8115</v>
+        <v>1.0535</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1614,10 +1614,10 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0912</v>
+        <v>0.1153</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1139</v>
+        <v>0.1479</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1107</v>
+        <v>0.1437</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.401</v>
+        <v>4.341</v>
       </c>
       <c r="E22" t="n">
         <v>5.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5744</v>
+        <v>1.2438</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
@@ -1794,10 +1794,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0674</v>
+        <v>0.1344</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2217</v>
+        <v>0.4801</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.209</v>
+        <v>0.4527</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.269</v>
+        <v>15.397</v>
       </c>
       <c r="E23" t="n">
         <v>14.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9758</v>
+        <v>0.9677</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1855,7 +1855,7 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1076</v>
+        <v>0.1068</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.0751</v>
+        <v>0.0745</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6514</v>
+        <v>0.6452</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1945,19 +1945,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0784</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7131</v>
+        <v>0.7551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6844</v>
+        <v>0.7306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6494</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="3">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8949</v>
+        <v>0.9369</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8844</v>
+        <v>0.9306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8716</v>
+        <v>0.9229000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1184</v>
+        <v>0.1231</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0768</v>
+        <v>1.1187</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0844</v>
+        <v>1.1306</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0938</v>
+        <v>1.1451</v>
       </c>
     </row>
     <row r="5">
@@ -2011,19 +2011,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1247</v>
+        <v>0.1216</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1047</v>
+        <v>0.1016</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9522</v>
+        <v>0.9241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9475</v>
+        <v>0.9165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9416</v>
+        <v>0.9072</v>
       </c>
     </row>
     <row r="6">
@@ -2033,19 +2033,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1247</v>
+        <v>0.1216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1247</v>
+        <v>0.1216</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1341</v>
+        <v>1.1059</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1475</v>
+        <v>1.1165</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1638</v>
+        <v>1.1294</v>
       </c>
     </row>
     <row r="7">
@@ -2055,19 +2055,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1247</v>
+        <v>0.1216</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1447</v>
+        <v>0.1416</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3159</v>
+        <v>1.2877</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3475</v>
+        <v>1.3165</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3861</v>
+        <v>1.3516</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.508</v>
+        <v>13.095</v>
       </c>
       <c r="E7" t="n">
         <v>16.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3111</v>
+        <v>1.2524</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1411</v>
+        <v>0.1352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1031</v>
+        <v>0.0984</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9306</v>
+        <v>0.8844</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.0964</v>
+        <v>0.092</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8636</v>
+        <v>0.8204</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.073</v>
+        <v>24.219</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2</v>
+        <v>34.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5082</v>
+        <v>1.4245</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2608</v>
+        <v>0.1524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.212</v>
+        <v>0.1051</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0201</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.1613</v>
+        <v>0.096</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5126</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.667</v>
+        <v>2.073</v>
       </c>
       <c r="E9" t="n">
-        <v>34.5</v>
+        <v>5.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.522</v>
+        <v>2.5082</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1622</v>
+        <v>0.2608</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1123</v>
+        <v>0.212</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0231</v>
+        <v>2.0201</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.1026</v>
+        <v>0.1613</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9262</v>
+        <v>1.5126</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32.16</v>
+        <v>34.559</v>
       </c>
       <c r="E10" t="n">
         <v>47.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4832</v>
+        <v>1.3802</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1583</v>
+        <v>0.148</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0823</v>
+        <v>0.0766</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6661</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0684</v>
+        <v>0.0636</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5837</v>
+        <v>0.5362</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>86.95399999999999</v>
+        <v>88.696</v>
       </c>
       <c r="E18" t="n">
         <v>37.14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4271</v>
+        <v>0.4187</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1553,7 +1553,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0527</v>
+        <v>0.0519</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.1345</v>
+        <v>0.1319</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2452</v>
+        <v>1.2188</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.581</v>
+        <v>15.592</v>
       </c>
       <c r="E19" t="n">
         <v>12.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0535</v>
+        <v>0.7825</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1614,10 +1614,10 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1153</v>
+        <v>0.0882</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1479</v>
+        <v>0.1098</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1437</v>
+        <v>0.1068</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4.341</v>
+        <v>9.401</v>
       </c>
       <c r="E22" t="n">
         <v>5.4</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2438</v>
+        <v>0.5744</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
@@ -1794,10 +1794,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1344</v>
+        <v>0.0674</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4801</v>
+        <v>0.2217</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4527</v>
+        <v>0.209</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.397</v>
+        <v>15.87</v>
       </c>
       <c r="E23" t="n">
         <v>14.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9677</v>
+        <v>0.9389</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1855,7 +1855,7 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1068</v>
+        <v>0.1039</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.0745</v>
+        <v>0.0723</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6452</v>
+        <v>0.623</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1945,19 +1945,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1031</v>
+        <v>0.0984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7551</v>
+        <v>0.7131</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7306</v>
+        <v>0.6844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7007</v>
+        <v>0.6494</v>
       </c>
     </row>
     <row r="3">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1031</v>
+        <v>0.0984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1031</v>
+        <v>0.0984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9369</v>
+        <v>0.8949</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9306</v>
+        <v>0.8844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.8716</v>
       </c>
     </row>
     <row r="4">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1031</v>
+        <v>0.0984</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1231</v>
+        <v>0.1184</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1187</v>
+        <v>1.0768</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1306</v>
+        <v>1.0844</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1451</v>
+        <v>1.0938</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.309</v>
+        <v>10.609</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6199</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1201</v>
+        <v>0.1414</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1009</v>
+        <v>1.3136</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0793</v>
+        <v>0.0946</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6933</v>
+        <v>0.8455</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.91</v>
+        <v>29.341</v>
       </c>
       <c r="E3" t="n">
         <v>27.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0108</v>
+        <v>0.927</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1111</v>
+        <v>0.1027</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1368</v>
+        <v>0.1334</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2682</v>
+        <v>1.234</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1161</v>
+        <v>0.1122</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0612</v>
+        <v>1.0222</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>flips (cheap/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -751,10 +751,10 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.081</v>
+        <v>0.0809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7096</v>
+        <v>0.7089</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2011,19 +2011,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1216</v>
+        <v>0.1283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1016</v>
+        <v>0.1083</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9241</v>
+        <v>0.9846</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9165</v>
+        <v>0.9831</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9072</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="6">
@@ -2033,19 +2033,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1216</v>
+        <v>0.1283</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1216</v>
+        <v>0.1283</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1059</v>
+        <v>1.1664</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1165</v>
+        <v>1.1831</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1294</v>
+        <v>1.2034</v>
       </c>
     </row>
     <row r="7">
@@ -2055,19 +2055,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1216</v>
+        <v>0.1283</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1416</v>
+        <v>0.1483</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2877</v>
+        <v>1.3482</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3165</v>
+        <v>1.3831</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3516</v>
+        <v>1.4256</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.609</v>
+        <v>10.469</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0702</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1414</v>
+        <v>0.1432</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3136</v>
+        <v>1.3325</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0946</v>
+        <v>0.0958</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8455</v>
+        <v>0.8581</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.592</v>
+        <v>15.493</v>
       </c>
       <c r="E19" t="n">
         <v>12.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7825</v>
+        <v>0.7874</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1614,10 +1614,10 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0882</v>
+        <v>0.0887</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1098</v>
+        <v>0.1105</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1068</v>
+        <v>0.1074</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.095</v>
+        <v>13.876</v>
       </c>
       <c r="E7" t="n">
         <v>16.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2524</v>
+        <v>1.1819</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1352</v>
+        <v>0.1282</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8844</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.092</v>
+        <v>0.0917</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8204</v>
+        <v>0.8172</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>0.1051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9512</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>0.0766</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6661</v>
+        <v>0.6662</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1945,19 +1945,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0784</v>
+        <v>0.078</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7131</v>
+        <v>0.7095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6844</v>
+        <v>0.6805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6494</v>
+        <v>0.6449</v>
       </c>
     </row>
     <row r="3">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8949</v>
+        <v>0.8913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8844</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8716</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="4">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1184</v>
+        <v>0.118</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0768</v>
+        <v>1.0731</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0844</v>
+        <v>1.0805</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0938</v>
+        <v>1.0894</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -817,7 +817,7 @@
         <v>0.0738</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6379</v>
+        <v>0.6377</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>0.1051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9512</v>
+        <v>0.951</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.073</v>
+        <v>2.793</v>
       </c>
       <c r="E9" t="n">
         <v>5.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5082</v>
+        <v>1.8616</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2608</v>
+        <v>0.1962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.212</v>
+        <v>0.1317</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0201</v>
+        <v>1.2167</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.1613</v>
+        <v>0.0983</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5126</v>
+        <v>0.8829</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>0.0766</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6662</v>
+        <v>0.6659</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.469</v>
+        <v>10.116</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6317</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1432</v>
+        <v>0.1515</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3325</v>
+        <v>1.4149</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0958</v>
+        <v>0.1013</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8581</v>
+        <v>0.9134</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.935</v>
+        <v>17.795</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0041</v>
+        <v>0.8991</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1492,7 +1492,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1104</v>
+        <v>0.0999</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0478</v>
+        <v>0.039</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3781</v>
+        <v>0.2898</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.401</v>
+        <v>8.798999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>5.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5744</v>
+        <v>0.6137</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
@@ -1794,10 +1794,10 @@
         <v>0.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0674</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2217</v>
+        <v>0.2368</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.209</v>
+        <v>0.2233</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34.559</v>
+        <v>34.352</v>
       </c>
       <c r="E10" t="n">
         <v>47.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3802</v>
+        <v>1.3886</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.148</v>
+        <v>0.1489</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0766</v>
+        <v>0.077</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6659</v>
+        <v>0.6705</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0636</v>
+        <v>0.064</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5362</v>
+        <v>0.5401</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.218</v>
+        <v>5.572</v>
       </c>
       <c r="E15" t="n">
         <v>7.7</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4758</v>
+        <v>1.382</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1370,7 +1370,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1576</v>
+        <v>0.1482</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.142</v>
+        <v>0.1316</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3201</v>
+        <v>1.2158</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80.35299999999999</v>
+        <v>77.46599999999999</v>
       </c>
       <c r="E14" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9408</v>
+        <v>0.9759</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
@@ -1309,7 +1309,7 @@
         <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1041</v>
+        <v>0.1076</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.0487</v>
+        <v>0.0463</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3872</v>
+        <v>0.363</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.435</v>
+        <v>30.344</v>
       </c>
       <c r="E16" t="n">
         <v>28.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1087</v>
+        <v>0.9293</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1431,7 +1431,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1209</v>
+        <v>0.1029</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.0863</v>
+        <v>0.0741</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7634</v>
+        <v>0.6414</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.023</v>
+        <v>2.041</v>
       </c>
       <c r="E20" t="n">
         <v>2.78</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3745</v>
+        <v>1.362</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1675,7 +1675,7 @@
         <v>0.015</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1456</v>
+        <v>0.1444</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.5</v>
+        <v>0.4955</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -610,10 +610,10 @@
         <v>29.341</v>
       </c>
       <c r="E3" t="n">
-        <v>27.2</v>
+        <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.8589</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,7 +622,7 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1027</v>
+        <v>0.0959</v>
       </c>
       <c r="J3" t="n">
         <v>0.1334</v>
@@ -656,7 +656,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.689</v>
+        <v>31.33</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9721</v>
+        <v>0.5506</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1072</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1232</v>
+        <v>0.0809</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1321</v>
+        <v>0.7089</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1117</v>
+        <v>0.0672</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0174</v>
+        <v>0.572</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.33</v>
+        <v>24.689</v>
       </c>
       <c r="E5" t="n">
-        <v>17.25</v>
+        <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5506</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.1092</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0809</v>
+        <v>0.1232</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7089</v>
+        <v>1.1321</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0672</v>
+        <v>0.1117</v>
       </c>
       <c r="N5" t="n">
-        <v>0.572</v>
+        <v>1.0174</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
         <v>77.51000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>70.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9134</v>
+        <v>0.8721</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,7 +811,7 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1013</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>0.0738</v>
@@ -862,10 +862,10 @@
         <v>13.876</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4</v>
+        <v>17.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1819</v>
+        <v>1.2395</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,7 +874,7 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1282</v>
+        <v>0.134</v>
       </c>
       <c r="J7" t="n">
         <v>0.098</v>
@@ -925,10 +925,10 @@
         <v>24.219</v>
       </c>
       <c r="E8" t="n">
-        <v>34.5</v>
+        <v>36.8</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4245</v>
+        <v>1.5194</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,7 +937,7 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1524</v>
+        <v>0.1619</v>
       </c>
       <c r="J8" t="n">
         <v>0.1051</v>
@@ -988,10 +988,10 @@
         <v>2.793</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8616</v>
+        <v>2.0764</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,7 +1000,7 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1962</v>
+        <v>0.2176</v>
       </c>
       <c r="J9" t="n">
         <v>0.1317</v>
@@ -1051,10 +1051,10 @@
         <v>34.352</v>
       </c>
       <c r="E10" t="n">
-        <v>47.7</v>
+        <v>53.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3886</v>
+        <v>1.5457</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,7 +1063,7 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1489</v>
+        <v>0.1646</v>
       </c>
       <c r="J10" t="n">
         <v>0.077</v>
@@ -1114,10 +1114,10 @@
         <v>52.589</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4832</v>
+        <v>1.5669</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,7 +1126,7 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1583</v>
+        <v>0.1667</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         <v>28.453</v>
       </c>
       <c r="E12" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0438</v>
+        <v>1.0298</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1187,7 +1187,7 @@
         <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1139</v>
+        <v>0.1127</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>28.097</v>
       </c>
       <c r="E13" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7794</v>
+        <v>0.7688</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
@@ -1248,7 +1248,7 @@
         <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0901</v>
+        <v>0.0892</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         <v>77.46599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9759</v>
+        <v>0.9424</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
@@ -1309,7 +1309,7 @@
         <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1076</v>
+        <v>0.1042</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         <v>5.572</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>1.382</v>
+        <v>1.2563</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1370,7 +1370,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1482</v>
+        <v>0.1356</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1419,10 +1419,10 @@
         <v>30.344</v>
       </c>
       <c r="E16" t="n">
-        <v>28.2</v>
+        <v>27.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9293</v>
+        <v>0.9129</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1431,7 +1431,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1029</v>
+        <v>0.1013</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1480,10 +1480,10 @@
         <v>17.795</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8991</v>
+        <v>0.8373</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1492,7 +1492,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0999</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         <v>15.493</v>
       </c>
       <c r="E19" t="n">
-        <v>12.2</v>
+        <v>13.31</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7874</v>
+        <v>0.8591</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1614,7 +1614,7 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0887</v>
+        <v>0.0959</v>
       </c>
       <c r="J19" t="n">
         <v>0.1105</v>
@@ -1663,10 +1663,10 @@
         <v>2.041</v>
       </c>
       <c r="E20" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="F20" t="n">
-        <v>1.362</v>
+        <v>1.1954</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1675,7 +1675,7 @@
         <v>0.015</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1444</v>
+        <v>0.1286</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>8.798999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6137</v>
+        <v>0.6024</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
@@ -1794,7 +1794,7 @@
         <v>0.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="J22" t="n">
         <v>0.2368</v>
@@ -1843,10 +1843,10 @@
         <v>15.87</v>
       </c>
       <c r="E23" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9389</v>
+        <v>0.92</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1855,7 +1855,7 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1039</v>
+        <v>0.102</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1879,128 @@
         </is>
       </c>
       <c r="Q23" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>34.109</v>
+      </c>
+      <c r="E24" t="n">
+        <v>36</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.0554</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BWLP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15.804</v>
+      </c>
+      <c r="E25" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.1719</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.2198</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>no anchor</t>
         </is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -625,10 +625,10 @@
         <v>0.0959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1334</v>
+        <v>0.1331</v>
       </c>
       <c r="K3" t="n">
-        <v>1.234</v>
+        <v>1.2308</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -688,10 +688,10 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0809</v>
+        <v>0.0805</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7089</v>
+        <v>0.7048</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>0.1092</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1232</v>
+        <v>0.1228</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1321</v>
+        <v>1.1277</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>dry_bulk</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77.51000000000001</v>
+        <v>0.385</v>
       </c>
       <c r="E6" t="n">
-        <v>67.59999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8721</v>
+        <v>1.0122</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,28 +811,28 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1112</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0738</v>
+        <v>0.124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6377</v>
+        <v>1.1405</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.0882</v>
+        <v>0.13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7818000000000001</v>
+        <v>1.1997</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.876</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2395</v>
+        <v>0.8721</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.134</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.098</v>
+        <v>0.0738</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.6377</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.0917</v>
+        <v>0.0882</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8172</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.219</v>
+        <v>13.876</v>
       </c>
       <c r="E8" t="n">
-        <v>36.8</v>
+        <v>17.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5194</v>
+        <v>1.2395</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1619</v>
+        <v>0.134</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1051</v>
+        <v>0.098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.951</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.096</v>
+        <v>0.0917</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8172</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.793</v>
+        <v>24.219</v>
       </c>
       <c r="E9" t="n">
-        <v>5.8</v>
+        <v>36.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0764</v>
+        <v>1.5194</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2176</v>
+        <v>0.1619</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1317</v>
+        <v>0.1051</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2167</v>
+        <v>0.951</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.0983</v>
+        <v>0.096</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8829</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34.352</v>
+        <v>2.793</v>
       </c>
       <c r="E10" t="n">
-        <v>53.1</v>
+        <v>5.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5457</v>
+        <v>2.0764</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1646</v>
+        <v>0.2176</v>
       </c>
       <c r="J10" t="n">
-        <v>0.077</v>
+        <v>0.1317</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6705</v>
+        <v>1.2167</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.064</v>
+        <v>0.0983</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5401</v>
+        <v>0.8829</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1097,12 +1097,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52.589</v>
+        <v>34.352</v>
       </c>
       <c r="E11" t="n">
-        <v>82.40000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5669</v>
+        <v>1.5457</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,18 +1126,24 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1667</v>
+        <v>0.1646</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6705</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>no anchor</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.0988</v>
+        <v>0.064</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8878</v>
+        <v>0.5401</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1146,48 +1152,44 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>no anchor</t>
-        </is>
-      </c>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.453</v>
+        <v>52.589</v>
       </c>
       <c r="E12" t="n">
-        <v>29.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0298</v>
+        <v>1.5669</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1127</v>
+        <v>0.1667</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1195,14 +1197,14 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.1465</v>
+        <v>0.0988</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4054</v>
+        <v>0.8878</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1219,7 +1221,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1233,13 +1235,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.097</v>
+        <v>28.453</v>
       </c>
       <c r="E13" t="n">
-        <v>21.6</v>
+        <v>29.3</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7688</v>
+        <v>1.0298</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
@@ -1248,7 +1250,7 @@
         <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0892</v>
+        <v>0.1127</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1256,10 +1258,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.2751</v>
+        <v>0.1465</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8347</v>
+        <v>1.4054</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1280,7 +1282,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1290,26 +1292,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77.46599999999999</v>
+        <v>28.097</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>21.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9424</v>
+        <v>0.7688</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1042</v>
+        <v>0.0892</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1317,14 +1319,14 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.0463</v>
+        <v>0.2751</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>2.8347</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1341,7 +1343,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1355,13 +1357,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.572</v>
+        <v>77.46599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2563</v>
+        <v>0.9424</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1370,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1356</v>
+        <v>0.1042</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1378,14 +1380,14 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.1316</v>
+        <v>0.0463</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2158</v>
+        <v>0.363</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1402,7 +1404,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1416,13 +1418,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30.344</v>
+        <v>5.572</v>
       </c>
       <c r="E16" t="n">
-        <v>27.7</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9129</v>
+        <v>1.2563</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1431,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1013</v>
+        <v>0.1356</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1439,14 +1441,14 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.0741</v>
+        <v>0.1316</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6414</v>
+        <v>1.2158</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1463,7 +1465,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1477,13 +1479,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.795</v>
+        <v>30.344</v>
       </c>
       <c r="E17" t="n">
-        <v>14.9</v>
+        <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8373</v>
+        <v>0.9129</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1492,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1500,10 +1502,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.039</v>
+        <v>0.0741</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2898</v>
+        <v>0.6414</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1524,27 +1526,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>product</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>88.696</v>
+        <v>17.795</v>
       </c>
       <c r="E18" t="n">
-        <v>37.14</v>
+        <v>14.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4187</v>
+        <v>0.8373</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1553,7 +1555,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0519</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1561,14 +1563,14 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.1319</v>
+        <v>0.039</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2188</v>
+        <v>0.2898</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1585,12 +1587,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1599,13 +1601,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.493</v>
+        <v>88.696</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31</v>
+        <v>37.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8591</v>
+        <v>0.4187</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1614,22 +1616,22 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0959</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.1105</v>
+        <v>0.0519</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1074</v>
+        <v>0.1319</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.2188</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1639,14 +1641,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1656,34 +1658,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>containerships</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.041</v>
+        <v>15.493</v>
       </c>
       <c r="E20" t="n">
-        <v>2.44</v>
+        <v>13.31</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1954</v>
+        <v>0.8591</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1286</v>
+        <v>0.0959</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1105</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>no anchor</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.4955</v>
+        <v>0.1074</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1697,14 +1702,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>no anchor</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1718,13 +1723,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.586</v>
+        <v>2.041</v>
       </c>
       <c r="E21" t="n">
-        <v>38.99</v>
+        <v>2.44</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0105</v>
+        <v>1.1954</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
@@ -1733,7 +1738,7 @@
         <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.111</v>
+        <v>0.1286</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1741,14 +1746,11 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.5108</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.219</v>
+        <v>0.4955</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1765,7 +1767,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,41 +1777,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>containerships</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.798999999999999</v>
+        <v>38.586</v>
       </c>
       <c r="E22" t="n">
-        <v>5.3</v>
+        <v>38.99</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6024</v>
+        <v>1.0105</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0702</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.2368</v>
+        <v>0.111</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.2233</v>
+        <v>0.5108</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.219</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1819,19 +1821,19 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>newbuild-heavy (unreliable)</t>
+          <t>no anchor</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1840,13 +1842,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.87</v>
+        <v>8.798999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>14.6</v>
+        <v>5.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.92</v>
+        <v>0.6024</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1855,22 +1857,22 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.102</v>
+        <v>0.0702</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2368</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>no anchor</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.0723</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.623</v>
+        <v>0.2233</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1880,34 +1882,34 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>no anchor</t>
+          <t>newbuild-heavy (unreliable)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lpg</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34.109</v>
+        <v>15.87</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>14.6</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0554</v>
+        <v>0.92</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1916,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1155</v>
+        <v>0.102</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1924,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.1013</v>
+        <v>0.0723</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9125</v>
+        <v>0.623</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1948,7 +1950,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1962,13 +1964,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.804</v>
+        <v>34.109</v>
       </c>
       <c r="E25" t="n">
-        <v>18.52</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1719</v>
+        <v>1.0554</v>
       </c>
       <c r="G25" t="n">
         <v>0.11</v>
@@ -1977,30 +1979,91 @@
         <v>0.01</v>
       </c>
       <c r="I25" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>rich</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BWLP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lpg</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.804</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.1719</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.1272</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>no anchor</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>no anchor</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>0.132</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>1.2198</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>fair</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>no anchor</t>
         </is>
@@ -2133,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1283</v>
+        <v>0.124</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1083</v>
+        <v>0.104</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9846</v>
+        <v>0.9459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9831</v>
+        <v>0.9405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9812</v>
+        <v>0.9339</v>
       </c>
     </row>
     <row r="6">
@@ -2155,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1283</v>
+        <v>0.124</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1283</v>
+        <v>0.124</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1664</v>
+        <v>1.1277</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1831</v>
+        <v>1.1405</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2034</v>
+        <v>1.1561</v>
       </c>
     </row>
     <row r="7">
@@ -2177,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1283</v>
+        <v>0.124</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1483</v>
+        <v>0.144</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3482</v>
+        <v>1.3095</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3831</v>
+        <v>1.3405</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4256</v>
+        <v>1.3783</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>88.696</v>
+        <v>88.761</v>
       </c>
       <c r="E19" t="n">
         <v>37.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4187</v>
+        <v>0.4184</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1616,7 +1616,7 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0519</v>
+        <v>0.0518</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1319</v>
+        <v>0.1318</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2188</v>
+        <v>1.2178</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -877,10 +877,10 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6377</v>
+        <v>0.6368</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>0.098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8797</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         <v>0.1619</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1051</v>
+        <v>0.105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.951</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         <v>0.2176</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1317</v>
+        <v>0.1314</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2167</v>
+        <v>1.2145</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0.1646</v>
       </c>
       <c r="J11" t="n">
-        <v>0.077</v>
+        <v>0.0769</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6705</v>
+        <v>0.6694</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>88.761</v>
+        <v>87.345</v>
       </c>
       <c r="E19" t="n">
         <v>37.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4184</v>
+        <v>0.4252</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1616,7 +1616,7 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0518</v>
+        <v>0.0525</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1318</v>
+        <v>0.1218</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2178</v>
+        <v>1.1176</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>0.0959</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1105</v>
+        <v>0.1104</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>0.0702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2368</v>
+        <v>0.2367</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>0.078</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7095</v>
+        <v>0.7088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6805</v>
+        <v>0.6797</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6449</v>
+        <v>0.6441</v>
       </c>
     </row>
     <row r="3">
@@ -2158,13 +2158,13 @@
         <v>0.098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8913</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8672</v>
+        <v>0.8663</v>
       </c>
     </row>
     <row r="4">
@@ -2180,13 +2180,13 @@
         <v>0.118</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0731</v>
+        <v>1.0725</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0805</v>
+        <v>1.0797</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0894</v>
+        <v>1.0886</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.116</v>
+        <v>10.166</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6317</v>
+        <v>0.6286</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0732</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1515</v>
+        <v>0.1507</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4149</v>
+        <v>1.4074</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1013</v>
+        <v>0.1008</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9134</v>
+        <v>0.9084</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.341</v>
+        <v>30.127</v>
       </c>
       <c r="E3" t="n">
         <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8589</v>
+        <v>0.8365</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0959</v>
+        <v>0.0936</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1331</v>
+        <v>0.1296</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2308</v>
+        <v>1.1961</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1122</v>
+        <v>0.1093</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0222</v>
+        <v>0.993</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.33</v>
+        <v>32.103</v>
       </c>
       <c r="E4" t="n">
         <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5506</v>
+        <v>0.5373</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0805</v>
+        <v>0.0785</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7048</v>
+        <v>0.6854</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.0672</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.572</v>
+        <v>0.5558</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.689</v>
+        <v>25.483</v>
       </c>
       <c r="E5" t="n">
         <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9614</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1092</v>
+        <v>0.1061</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1228</v>
+        <v>0.1189</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1277</v>
+        <v>1.0894</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1117</v>
+        <v>0.1083</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0174</v>
+        <v>0.9825</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="E6" t="n">
         <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0122</v>
+        <v>0.9918</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1112</v>
+        <v>0.1092</v>
       </c>
       <c r="J6" t="n">
-        <v>0.124</v>
+        <v>0.1215</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1405</v>
+        <v>1.1154</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.13</v>
+        <v>0.1273</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1997</v>
+        <v>1.1735</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>77.729</v>
       </c>
       <c r="E7" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8721</v>
+        <v>0.8697</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0737</v>
+        <v>0.0735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6368</v>
+        <v>0.6347</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.0882</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7793</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.876</v>
+        <v>13.584</v>
       </c>
       <c r="E8" t="n">
         <v>17.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2395</v>
+        <v>1.2662</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.134</v>
+        <v>0.1366</v>
       </c>
       <c r="J8" t="n">
-        <v>0.098</v>
+        <v>0.1001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8797</v>
+        <v>0.9008</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0917</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8172</v>
+        <v>0.8369</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.219</v>
+        <v>24.107</v>
       </c>
       <c r="E9" t="n">
         <v>36.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5194</v>
+        <v>1.5265</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1619</v>
+        <v>0.1627</v>
       </c>
       <c r="J9" t="n">
-        <v>0.105</v>
+        <v>0.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.096</v>
+        <v>0.0965</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8648</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.793</v>
+        <v>2.845</v>
       </c>
       <c r="E10" t="n">
         <v>5.8</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0764</v>
+        <v>2.0387</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2176</v>
+        <v>0.2139</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1314</v>
+        <v>0.1291</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2145</v>
+        <v>1.1906</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0983</v>
+        <v>0.0965</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8829</v>
+        <v>0.865</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34.352</v>
+        <v>34.423</v>
       </c>
       <c r="E11" t="n">
         <v>53.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5457</v>
+        <v>1.5426</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,13 +1126,13 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1646</v>
+        <v>0.1643</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0769</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6694</v>
+        <v>0.6679</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.064</v>
+        <v>0.0639</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5401</v>
+        <v>0.5387</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52.589</v>
+        <v>52.477</v>
       </c>
       <c r="E12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5669</v>
+        <v>1.5702</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1189,7 +1189,7 @@
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1667</v>
+        <v>0.167</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.0988</v>
+        <v>0.099</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8878</v>
+        <v>0.89</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.46599999999999</v>
+        <v>77.133</v>
       </c>
       <c r="E15" t="n">
         <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9424</v>
+        <v>0.9464</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1372,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1042</v>
+        <v>0.1046</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.0463</v>
+        <v>0.0465</v>
       </c>
       <c r="N15" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.572</v>
+        <v>5.571</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2563</v>
+        <v>1.2566</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1433,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1356</v>
+        <v>0.1357</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>0.1316</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2158</v>
+        <v>1.2161</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.344</v>
+        <v>30.303</v>
       </c>
       <c r="E17" t="n">
         <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9129</v>
+        <v>0.9141</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1494,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1013</v>
+        <v>0.1014</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0741</v>
+        <v>0.0742</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6414</v>
+        <v>0.6424</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.795</v>
+        <v>17.816</v>
       </c>
       <c r="E18" t="n">
         <v>14.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8373</v>
+        <v>0.8363</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1555,7 +1555,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0936</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.039</v>
+        <v>0.0389</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2898</v>
+        <v>0.2893</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>87.345</v>
+        <v>87.56699999999999</v>
       </c>
       <c r="E19" t="n">
         <v>37.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4252</v>
+        <v>0.4241</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1616,7 +1616,7 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0525</v>
+        <v>0.0524</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1218</v>
+        <v>0.1215</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1176</v>
+        <v>1.1146</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.493</v>
+        <v>15.488</v>
       </c>
       <c r="E20" t="n">
         <v>13.31</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8591</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.1074</v>
+        <v>0.1075</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.87</v>
+        <v>16.121</v>
       </c>
       <c r="E24" t="n">
         <v>14.6</v>
       </c>
       <c r="F24" t="n">
-        <v>0.92</v>
+        <v>0.9056</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.102</v>
+        <v>0.1006</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0723</v>
+        <v>0.0712</v>
       </c>
       <c r="N24" t="n">
-        <v>0.623</v>
+        <v>0.6117</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.098</v>
+        <v>0.1001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.078</v>
+        <v>0.0801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7088</v>
+        <v>0.728</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6797</v>
+        <v>0.7008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6441</v>
+        <v>0.6675</v>
       </c>
     </row>
     <row r="3">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.098</v>
+        <v>0.1001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.098</v>
+        <v>0.1001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8797</v>
+        <v>0.9008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8663</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="4">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.098</v>
+        <v>0.1001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.118</v>
+        <v>0.1201</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0725</v>
+        <v>1.0916</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0797</v>
+        <v>1.1008</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0886</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="5">
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.124</v>
+        <v>0.1215</v>
       </c>
       <c r="C5" t="n">
-        <v>0.104</v>
+        <v>0.1015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9459</v>
+        <v>0.9231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9405</v>
+        <v>0.9154</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9339</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.124</v>
+        <v>0.1215</v>
       </c>
       <c r="C6" t="n">
-        <v>0.124</v>
+        <v>0.1215</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1277</v>
+        <v>1.1049</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1405</v>
+        <v>1.1154</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1561</v>
+        <v>1.1283</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.124</v>
+        <v>0.1215</v>
       </c>
       <c r="C7" t="n">
-        <v>0.144</v>
+        <v>0.1415</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3095</v>
+        <v>1.2868</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3405</v>
+        <v>1.3154</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3783</v>
+        <v>1.3505</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.166</v>
+        <v>10.019</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6286</v>
+        <v>0.6378</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1507</v>
+        <v>0.153</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4074</v>
+        <v>1.4295</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1008</v>
+        <v>0.1023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9084</v>
+        <v>0.9232</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.019</v>
+        <v>10.072</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6378</v>
+        <v>0.6345</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0738</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.153</v>
+        <v>0.1522</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4295</v>
+        <v>1.4215</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1023</v>
+        <v>0.1018</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9232</v>
+        <v>0.9179</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.127</v>
+        <v>30.639</v>
       </c>
       <c r="E3" t="n">
         <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8365</v>
+        <v>0.8225</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0936</v>
+        <v>0.0922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1296</v>
+        <v>0.1274</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1961</v>
+        <v>1.1744</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1093</v>
+        <v>0.1075</v>
       </c>
       <c r="N3" t="n">
-        <v>0.993</v>
+        <v>0.9747</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.103</v>
+        <v>32.65</v>
       </c>
       <c r="E4" t="n">
         <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5373</v>
+        <v>0.5283</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0785</v>
+        <v>0.0772</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6854</v>
+        <v>0.6722</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0645</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5558</v>
+        <v>0.5448</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.483</v>
+        <v>25.981</v>
       </c>
       <c r="E5" t="n">
         <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9614</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1061</v>
+        <v>0.1043</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1189</v>
+        <v>0.1167</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0894</v>
+        <v>1.0666</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1083</v>
+        <v>0.1062</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9825</v>
+        <v>0.9618</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.393</v>
+        <v>0.399</v>
       </c>
       <c r="E6" t="n">
         <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9918</v>
+        <v>0.9764</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1092</v>
+        <v>0.1076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1215</v>
+        <v>0.1197</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1154</v>
+        <v>1.0965</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1273</v>
+        <v>0.1254</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1735</v>
+        <v>1.1537</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.121</v>
+        <v>16.191</v>
       </c>
       <c r="E24" t="n">
         <v>14.6</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9056</v>
+        <v>0.9018</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1006</v>
+        <v>0.1002</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0712</v>
+        <v>0.0709</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6117</v>
+        <v>0.6086</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1215</v>
+        <v>0.1197</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1015</v>
+        <v>0.0997</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9231</v>
+        <v>0.906</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9154</v>
+        <v>0.8965</v>
       </c>
       <c r="F5" t="n">
-        <v>0.906</v>
+        <v>0.8851</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1215</v>
+        <v>0.1197</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1215</v>
+        <v>0.1197</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1049</v>
+        <v>1.0878</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1154</v>
+        <v>1.0965</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1283</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1215</v>
+        <v>0.1197</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1415</v>
+        <v>0.1397</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2868</v>
+        <v>1.2696</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3154</v>
+        <v>1.2965</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3505</v>
+        <v>1.3295</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.072</v>
+        <v>10.727</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6345</v>
+        <v>0.5957</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1522</v>
+        <v>0.1459</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4215</v>
+        <v>1.3593</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1018</v>
+        <v>0.0978</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9179</v>
+        <v>0.8782</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.729</v>
+        <v>81.47799999999999</v>
       </c>
       <c r="E7" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8697</v>
+        <v>0.8297</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.097</v>
+        <v>0.093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0735</v>
+        <v>0.0716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6347</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0848</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7793</v>
+        <v>0.7478</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (rich/fair)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -943,7 +943,7 @@
         <v>0.1001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9008</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.955</v>
+        <v>0.9549</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>0.1291</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1906</v>
+        <v>1.1905</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6679</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>0.0702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2367</v>
+        <v>0.2366</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>0.0801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.728</v>
+        <v>0.7279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7008</v>
+        <v>0.7007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6675</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="3">
@@ -2158,13 +2158,13 @@
         <v>0.1001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9097</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8897</v>
+        <v>0.8895999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2180,13 +2180,13 @@
         <v>0.1201</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0916</v>
+        <v>1.0915</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1008</v>
+        <v>1.1007</v>
       </c>
       <c r="F4" t="n">
-        <v>1.112</v>
+        <v>1.1119</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.727</v>
+        <v>10.072</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5957</v>
+        <v>0.6345</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0696</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1459</v>
+        <v>0.1522</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3593</v>
+        <v>1.4215</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0978</v>
+        <v>0.1018</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8782</v>
+        <v>0.9179</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.47799999999999</v>
+        <v>77.729</v>
       </c>
       <c r="E7" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8297</v>
+        <v>0.8697</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.093</v>
+        <v>0.097</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0716</v>
+        <v>0.0735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6347</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.0848</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7478</v>
+        <v>0.7793</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>flips (rich/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -943,7 +943,7 @@
         <v>0.1001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9008</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9549</v>
+        <v>0.955</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>0.1291</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1905</v>
+        <v>1.1906</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6679</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>0.0702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2366</v>
+        <v>0.2367</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>0.0801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7279</v>
+        <v>0.728</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7007</v>
+        <v>0.7008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6674</v>
+        <v>0.6675</v>
       </c>
     </row>
     <row r="3">
@@ -2158,13 +2158,13 @@
         <v>0.1001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9097</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="4">
@@ -2180,13 +2180,13 @@
         <v>0.1201</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0915</v>
+        <v>1.0916</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1007</v>
+        <v>1.1008</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1119</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.072</v>
+        <v>10.035</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6345</v>
+        <v>0.6368</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1522</v>
+        <v>0.156</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4215</v>
+        <v>1.4599</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1018</v>
+        <v>0.1046</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9179</v>
+        <v>0.9457</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.729</v>
+        <v>84.60299999999999</v>
       </c>
       <c r="E7" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8697</v>
+        <v>0.799</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,13 +874,13 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.097</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0735</v>
+        <v>0.0689</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6347</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7793</v>
+        <v>0.7156</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>0.1001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9008</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.955</v>
+        <v>0.9549</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>0.1291</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1906</v>
+        <v>1.1905</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6679</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.816</v>
+        <v>17.373</v>
       </c>
       <c r="E18" t="n">
         <v>14.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8363</v>
+        <v>0.8576</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1555,7 +1555,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0936</v>
+        <v>0.0958</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.0389</v>
+        <v>0.0721</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2893</v>
+        <v>0.6209</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>0.0702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2367</v>
+        <v>0.2366</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>0.0801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.728</v>
+        <v>0.7279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7008</v>
+        <v>0.7007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6675</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="3">
@@ -2158,13 +2158,13 @@
         <v>0.1001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9097</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9008</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8897</v>
+        <v>0.8895999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2180,13 +2180,13 @@
         <v>0.1201</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0916</v>
+        <v>1.0915</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1008</v>
+        <v>1.1007</v>
       </c>
       <c r="F4" t="n">
-        <v>1.112</v>
+        <v>1.1119</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.845</v>
+        <v>37.649</v>
       </c>
       <c r="E10" t="n">
-        <v>5.8</v>
+        <v>53.1</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0387</v>
+        <v>1.4104</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2139</v>
+        <v>0.151</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1291</v>
+        <v>0.0702</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1905</v>
+        <v>0.602</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0965</v>
+        <v>0.0584</v>
       </c>
       <c r="N10" t="n">
-        <v>0.865</v>
+        <v>0.484</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34.423</v>
+        <v>2.845</v>
       </c>
       <c r="E11" t="n">
-        <v>53.1</v>
+        <v>5.8</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5426</v>
+        <v>2.0387</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,13 +1126,13 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1643</v>
+        <v>0.2139</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1291</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6677999999999999</v>
+        <v>1.1905</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.0639</v>
+        <v>0.0965</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5387</v>
+        <v>0.865</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.097</v>
+        <v>25.702</v>
       </c>
       <c r="E14" t="n">
         <v>21.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7688</v>
+        <v>0.8404</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
@@ -1311,7 +1311,7 @@
         <v>0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0892</v>
+        <v>0.0956</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2751</v>
+        <v>0.3001</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8347</v>
+        <v>3.1124</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1006,7 +1006,7 @@
         <v>0.1055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9549</v>
+        <v>0.9545</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.133</v>
+        <v>76.423</v>
       </c>
       <c r="E15" t="n">
         <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9464</v>
+        <v>0.9552</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1372,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1046</v>
+        <v>0.1055</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.0465</v>
+        <v>0.0347</v>
       </c>
       <c r="N15" t="n">
-        <v>0.365</v>
+        <v>0.2472</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34.109</v>
+        <v>35.691</v>
       </c>
       <c r="E25" t="n">
         <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0554</v>
+        <v>1.0087</v>
       </c>
       <c r="G25" t="n">
         <v>0.11</v>
@@ -1979,7 +1979,7 @@
         <v>0.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1155</v>
+        <v>0.1109</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.1013</v>
+        <v>0.0694</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9125</v>
+        <v>0.5938</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.586</v>
+        <v>41.204</v>
       </c>
       <c r="E22" t="n">
         <v>38.99</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0105</v>
+        <v>0.9463</v>
       </c>
       <c r="G22" t="n">
         <v>0.11</v>
@@ -1796,7 +1796,7 @@
         <v>0.015</v>
       </c>
       <c r="I22" t="n">
-        <v>0.111</v>
+        <v>0.1049</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.5108</v>
+        <v>0.4784</v>
       </c>
       <c r="N22" t="n">
-        <v>5.219</v>
+        <v>4.8774</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.584</v>
+        <v>13.826</v>
       </c>
       <c r="E8" t="n">
         <v>17.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2662</v>
+        <v>1.244</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1366</v>
+        <v>0.1344</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1001</v>
+        <v>0.0982</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0919</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8369</v>
+        <v>0.8194</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1001</v>
+        <v>0.0982</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0801</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7279</v>
+        <v>0.7109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7007</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6674</v>
+        <v>0.6467000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1001</v>
+        <v>0.0982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1001</v>
+        <v>0.0982</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9097</v>
+        <v>0.8927</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8689</v>
       </c>
     </row>
     <row r="4">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1001</v>
+        <v>0.0982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1201</v>
+        <v>0.1182</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0915</v>
+        <v>1.0745</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1007</v>
+        <v>1.082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1119</v>
+        <v>1.0911</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -565,7 +565,7 @@
         <v>0.156</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4599</v>
+        <v>1.4602</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.65</v>
+        <v>25.255</v>
       </c>
       <c r="E4" t="n">
-        <v>17.25</v>
+        <v>24.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5283</v>
+        <v>0.9701</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0772</v>
+        <v>0.1227</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6722</v>
+        <v>1.1275</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.0645</v>
+        <v>0.1112</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5448</v>
+        <v>1.0124</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.981</v>
+        <v>32.65</v>
       </c>
       <c r="E5" t="n">
-        <v>24.5</v>
+        <v>17.25</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.5283</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1043</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1167</v>
+        <v>0.0772</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0666</v>
+        <v>0.672</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1062</v>
+        <v>0.0645</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9618</v>
+        <v>0.5448</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         <v>0.1076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1197</v>
+        <v>0.1196</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0965</v>
+        <v>1.096</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1197</v>
+        <v>0.1227</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0997</v>
+        <v>0.1027</v>
       </c>
       <c r="D5" t="n">
-        <v>0.906</v>
+        <v>0.9341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8965</v>
+        <v>0.9275</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8851</v>
+        <v>0.9194</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1197</v>
+        <v>0.1227</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1197</v>
+        <v>0.1227</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0878</v>
+        <v>1.1159</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0965</v>
+        <v>1.1275</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1073</v>
+        <v>1.1416</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1197</v>
+        <v>0.1227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1397</v>
+        <v>0.1427</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2696</v>
+        <v>1.2977</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2965</v>
+        <v>1.3275</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3295</v>
+        <v>1.3639</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.399</v>
+        <v>0.411</v>
       </c>
       <c r="E6" t="n">
         <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9764</v>
+        <v>0.9499</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1076</v>
+        <v>0.105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1196</v>
+        <v>0.1189</v>
       </c>
       <c r="K6" t="n">
-        <v>1.096</v>
+        <v>1.0892</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1254</v>
+        <v>0.1247</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1537</v>
+        <v>1.1466</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -562,10 +562,10 @@
         <v>0.0737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.156</v>
+        <v>0.1561</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4602</v>
+        <v>1.4613</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.639</v>
+        <v>32.392</v>
       </c>
       <c r="E3" t="n">
         <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8225</v>
+        <v>0.778</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0922</v>
+        <v>0.0878</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1274</v>
+        <v>0.1231</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1744</v>
+        <v>1.1307</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1075</v>
+        <v>0.1042</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9747</v>
+        <v>0.9425</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>0.0772</v>
       </c>
       <c r="K5" t="n">
-        <v>0.672</v>
+        <v>0.6724</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.65</v>
+        <v>31.921</v>
       </c>
       <c r="E5" t="n">
         <v>17.25</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5283</v>
+        <v>0.5404</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0772</v>
+        <v>0.0788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6724</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0645</v>
+        <v>0.0658</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5448</v>
+        <v>0.5579</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.035</v>
+        <v>10.579</v>
       </c>
       <c r="E2" t="n">
         <v>6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6368</v>
+        <v>0.604</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0737</v>
+        <v>0.0704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1561</v>
+        <v>0.1481</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4613</v>
+        <v>1.3809</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1046</v>
+        <v>0.0992</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9457</v>
+        <v>0.8919</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.392</v>
+        <v>33.038</v>
       </c>
       <c r="E3" t="n">
         <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.778</v>
+        <v>0.7628</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0878</v>
+        <v>0.0863</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1231</v>
+        <v>0.1207</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1307</v>
+        <v>1.1067</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1042</v>
+        <v>0.1022</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9425</v>
+        <v>0.9221</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.255</v>
+        <v>25.376</v>
       </c>
       <c r="E4" t="n">
         <v>24.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9701</v>
+        <v>0.9655</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.107</v>
+        <v>0.1065</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1227</v>
+        <v>0.1222</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1275</v>
+        <v>1.1216</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1112</v>
+        <v>0.1107</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0124</v>
+        <v>1.0072</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.921</v>
+        <v>32.425</v>
       </c>
       <c r="E5" t="n">
         <v>17.25</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5404</v>
+        <v>0.532</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.064</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0788</v>
+        <v>0.0776</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6758</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0658</v>
+        <v>0.0648</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5579</v>
+        <v>0.5477</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9499</v>
+        <v>0.9492</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.105</v>
+        <v>0.1049</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1189</v>
+        <v>0.1188</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0892</v>
+        <v>1.0883</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1247</v>
+        <v>0.1246</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1466</v>
+        <v>1.1456</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.826</v>
+        <v>15.005</v>
       </c>
       <c r="E8" t="n">
         <v>17.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.244</v>
+        <v>1.1463</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,13 +937,13 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1344</v>
+        <v>0.1246</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0982</v>
+        <v>0.0905</v>
       </c>
       <c r="K8" t="n">
-        <v>0.882</v>
+        <v>0.8048</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0919</v>
+        <v>0.0847</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8194</v>
+        <v>0.7472</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.107</v>
+        <v>25.337</v>
       </c>
       <c r="E9" t="n">
         <v>36.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5265</v>
+        <v>1.4524</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1627</v>
+        <v>0.1552</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1055</v>
+        <v>0.1003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9545</v>
+        <v>0.9034</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.0965</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8648</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37.649</v>
+        <v>39.537</v>
       </c>
       <c r="E10" t="n">
         <v>53.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4104</v>
+        <v>1.343</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,13 +1063,13 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.151</v>
+        <v>0.1443</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0702</v>
+        <v>0.0668</v>
       </c>
       <c r="K10" t="n">
-        <v>0.602</v>
+        <v>0.5685</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0584</v>
+        <v>0.0556</v>
       </c>
       <c r="N10" t="n">
-        <v>0.484</v>
+        <v>0.4561</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52.477</v>
+        <v>53.881</v>
       </c>
       <c r="E12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5702</v>
+        <v>1.5293</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1189,7 +1189,7 @@
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.167</v>
+        <v>0.1629</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.099</v>
+        <v>0.0964</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.8642</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76.423</v>
+        <v>76.22</v>
       </c>
       <c r="E15" t="n">
         <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9552</v>
+        <v>0.9578</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1372,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1055</v>
+        <v>0.1058</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.0347</v>
+        <v>0.0348</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2472</v>
+        <v>0.2482</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.571</v>
+        <v>5.565</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2566</v>
+        <v>1.258</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1433,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1357</v>
+        <v>0.1358</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.1316</v>
+        <v>0.1318</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2161</v>
+        <v>1.2175</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.303</v>
+        <v>30.219</v>
       </c>
       <c r="E17" t="n">
         <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9141</v>
+        <v>0.9167</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1494,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1014</v>
+        <v>0.1017</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0742</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6424</v>
+        <v>0.6445</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>87.56699999999999</v>
+        <v>88.15600000000001</v>
       </c>
       <c r="E19" t="n">
         <v>37.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4241</v>
+        <v>0.4213</v>
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
@@ -1616,7 +1616,7 @@
         <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0524</v>
+        <v>0.0521</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1215</v>
+        <v>0.1206</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1146</v>
+        <v>1.1064</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.488</v>
+        <v>15.482</v>
       </c>
       <c r="E20" t="n">
         <v>13.31</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8597</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1677,10 +1677,10 @@
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0959</v>
+        <v>0.096</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1104</v>
+        <v>0.1105</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.191</v>
+        <v>16.457</v>
       </c>
       <c r="E24" t="n">
         <v>14.6</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9018</v>
+        <v>0.8871</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1002</v>
+        <v>0.0987</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0709</v>
+        <v>0.0697</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6086</v>
+        <v>0.5972</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0982</v>
+        <v>0.0905</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7109</v>
+        <v>0.6407</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.5609</v>
       </c>
     </row>
     <row r="3">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0982</v>
+        <v>0.0905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0982</v>
+        <v>0.0905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8927</v>
+        <v>0.8226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.882</v>
+        <v>0.8048</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8689</v>
+        <v>0.7831</v>
       </c>
     </row>
     <row r="4">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0982</v>
+        <v>0.0905</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1182</v>
+        <v>0.1105</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0745</v>
+        <v>1.0044</v>
       </c>
       <c r="E4" t="n">
-        <v>1.082</v>
+        <v>1.0048</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0911</v>
+        <v>1.0053</v>
       </c>
     </row>
     <row r="5">
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1227</v>
+        <v>0.1207</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1027</v>
+        <v>0.1007</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9341</v>
+        <v>0.9152</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9275</v>
+        <v>0.9067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9194</v>
+        <v>0.8963</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1227</v>
+        <v>0.1207</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1227</v>
+        <v>0.1207</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1159</v>
+        <v>1.097</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1275</v>
+        <v>1.1067</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1416</v>
+        <v>1.1185</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1227</v>
+        <v>0.1207</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1427</v>
+        <v>0.1407</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2977</v>
+        <v>1.2788</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3275</v>
+        <v>1.3067</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3639</v>
+        <v>1.3408</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.041</v>
+        <v>2.05</v>
       </c>
       <c r="E21" t="n">
         <v>2.44</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1954</v>
+        <v>1.19</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
@@ -1738,7 +1738,7 @@
         <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1286</v>
+        <v>0.1281</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4955</v>
+        <v>0.4932</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.038</v>
+        <v>32.785</v>
       </c>
       <c r="E3" t="n">
         <v>25.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7628</v>
+        <v>0.7687</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0863</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1207</v>
+        <v>0.1216</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1067</v>
+        <v>1.116</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1022</v>
+        <v>0.103</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9221</v>
+        <v>0.93</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.376</v>
+        <v>25.118</v>
       </c>
       <c r="E4" t="n">
         <v>24.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9655</v>
+        <v>0.9754</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1065</v>
+        <v>0.1075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1222</v>
+        <v>0.1234</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1216</v>
+        <v>1.1342</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1107</v>
+        <v>0.1119</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0072</v>
+        <v>1.0185</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.425</v>
+        <v>32.133</v>
       </c>
       <c r="E5" t="n">
         <v>17.25</v>
       </c>
       <c r="F5" t="n">
-        <v>0.532</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0776</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6758</v>
+        <v>0.6828</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0648</v>
+        <v>0.0654</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5477</v>
+        <v>0.5536</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.411</v>
+        <v>0.407</v>
       </c>
       <c r="E6" t="n">
         <v>0.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9492</v>
+        <v>0.9583</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1049</v>
+        <v>0.1058</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1188</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0883</v>
+        <v>1.0997</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1246</v>
+        <v>0.1258</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1456</v>
+        <v>1.1576</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1207</v>
+        <v>0.1216</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1007</v>
+        <v>0.1016</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9152</v>
+        <v>0.9237</v>
       </c>
       <c r="E5" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.9067</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8963</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1207</v>
+        <v>0.1216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1207</v>
+        <v>0.1216</v>
       </c>
       <c r="D6" t="n">
-        <v>1.097</v>
+        <v>1.1055</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1067</v>
+        <v>1.116</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1185</v>
+        <v>1.1289</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1207</v>
+        <v>0.1216</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1407</v>
+        <v>0.1416</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2788</v>
+        <v>1.2873</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3067</v>
+        <v>1.316</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3408</v>
+        <v>1.3511</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.881</v>
+        <v>54.638</v>
       </c>
       <c r="E12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5293</v>
+        <v>1.5081</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1189,7 +1189,7 @@
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1629</v>
+        <v>0.1608</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.0964</v>
+        <v>0.0973</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8642</v>
+        <v>0.8733</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8.798999999999999</v>
+        <v>9.622</v>
       </c>
       <c r="E23" t="n">
         <v>5.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6024</v>
+        <v>0.5508</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1857,10 +1857,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0702</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2366</v>
+        <v>0.2164</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.2233</v>
+        <v>0.2042</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -610,10 +610,10 @@
         <v>32.785</v>
       </c>
       <c r="E3" t="n">
-        <v>25.2</v>
+        <v>28.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7687</v>
+        <v>0.8724</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,7 +622,7 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>0.1216</v>
@@ -643,12 +643,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (cheap/fair)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -656,7 +656,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.118</v>
+        <v>32.133</v>
       </c>
       <c r="E4" t="n">
-        <v>24.5</v>
+        <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9754</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1075</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1234</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1342</v>
+        <v>0.6828</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1119</v>
+        <v>0.0654</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0185</v>
+        <v>0.5536</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.133</v>
+        <v>0.407</v>
       </c>
       <c r="E5" t="n">
-        <v>17.25</v>
+        <v>0.39</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.9583</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.1058</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6828</v>
+        <v>1.0997</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0654</v>
+        <v>0.1258</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5536</v>
+        <v>1.1576</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>flips (cheap/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.407</v>
+        <v>25.118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.39</v>
+        <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9583</v>
+        <v>0.9993</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1058</v>
+        <v>0.1099</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>0.1234</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0997</v>
+        <v>1.1342</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,19 +825,19 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1258</v>
+        <v>0.1119</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1576</v>
+        <v>1.0185</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (cheap/fair)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -862,10 +862,10 @@
         <v>84.60299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>67.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.799</v>
+        <v>0.9113</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,7 +874,7 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1011</v>
       </c>
       <c r="J7" t="n">
         <v>0.0689</v>
@@ -925,10 +925,10 @@
         <v>15.005</v>
       </c>
       <c r="E8" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1463</v>
+        <v>1.2262</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,7 +937,7 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1246</v>
+        <v>0.1326</v>
       </c>
       <c r="J8" t="n">
         <v>0.0905</v>
@@ -988,10 +988,10 @@
         <v>25.337</v>
       </c>
       <c r="E9" t="n">
-        <v>36.8</v>
+        <v>39.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4524</v>
+        <v>1.5629</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,7 +1000,7 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1552</v>
+        <v>0.1663</v>
       </c>
       <c r="J9" t="n">
         <v>0.1003</v>
@@ -1051,10 +1051,10 @@
         <v>39.537</v>
       </c>
       <c r="E10" t="n">
-        <v>53.1</v>
+        <v>63.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.343</v>
+        <v>1.6137</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,7 +1063,7 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1443</v>
+        <v>0.1714</v>
       </c>
       <c r="J10" t="n">
         <v>0.0668</v>
@@ -1114,10 +1114,10 @@
         <v>2.845</v>
       </c>
       <c r="E11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0387</v>
+        <v>2.2495</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,7 +1126,7 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2139</v>
+        <v>0.235</v>
       </c>
       <c r="J11" t="n">
         <v>0.1291</v>
@@ -1177,10 +1177,10 @@
         <v>54.638</v>
       </c>
       <c r="E12" t="n">
-        <v>82.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5081</v>
+        <v>1.7058</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1189,7 +1189,7 @@
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1608</v>
+        <v>0.1806</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         <v>28.453</v>
       </c>
       <c r="E13" t="n">
-        <v>29.3</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0298</v>
+        <v>1.0895</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
@@ -1250,7 +1250,7 @@
         <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1127</v>
+        <v>0.1181</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         <v>25.702</v>
       </c>
       <c r="E14" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8404</v>
+        <v>0.8871</v>
       </c>
       <c r="G14" t="n">
         <v>0.11</v>
@@ -1311,7 +1311,7 @@
         <v>0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0956</v>
+        <v>0.0998</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         <v>76.22</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9578</v>
+        <v>1.0024</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1372,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1058</v>
+        <v>0.1102</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         <v>5.565</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1.258</v>
+        <v>1.3658</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1433,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1358</v>
+        <v>0.1466</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1482,10 +1482,10 @@
         <v>30.219</v>
       </c>
       <c r="E17" t="n">
-        <v>27.7</v>
+        <v>29.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9167</v>
+        <v>0.9762</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1494,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1017</v>
+        <v>0.1076</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>17.373</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8576</v>
+        <v>0.9785</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1555,7 +1555,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0958</v>
+        <v>0.1079</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>15.482</v>
       </c>
       <c r="E20" t="n">
-        <v>13.31</v>
+        <v>14.14</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8597</v>
+        <v>0.9133</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1677,7 +1677,7 @@
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.096</v>
+        <v>0.1013</v>
       </c>
       <c r="J20" t="n">
         <v>0.1105</v>
@@ -1726,10 +1726,10 @@
         <v>2.05</v>
       </c>
       <c r="E21" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="F21" t="n">
-        <v>1.19</v>
+        <v>1.2437</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
@@ -1738,7 +1738,7 @@
         <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1281</v>
+        <v>0.1331</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         <v>9.622</v>
       </c>
       <c r="E23" t="n">
-        <v>5.3</v>
+        <v>6.32</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5508</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1857,7 +1857,7 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="J23" t="n">
         <v>0.2164</v>
@@ -1906,10 +1906,10 @@
         <v>16.457</v>
       </c>
       <c r="E24" t="n">
-        <v>14.6</v>
+        <v>16.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8871</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0987</v>
+        <v>0.1097</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         <v>35.691</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>44.4</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0087</v>
+        <v>1.244</v>
       </c>
       <c r="G25" t="n">
         <v>0.11</v>
@@ -1979,7 +1979,7 @@
         <v>0.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1109</v>
+        <v>0.1344</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         <v>15.804</v>
       </c>
       <c r="E26" t="n">
-        <v>18.52</v>
+        <v>21.77</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1719</v>
+        <v>1.3775</v>
       </c>
       <c r="G26" t="n">
         <v>0.11</v>
@@ -2040,7 +2040,7 @@
         <v>0.01</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1272</v>
+        <v>0.1478</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.453</v>
+        <v>27.222</v>
       </c>
       <c r="E13" t="n">
         <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0895</v>
+        <v>1.1388</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
@@ -1250,7 +1250,7 @@
         <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1181</v>
+        <v>0.1225</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.1465</v>
+        <v>0.1531</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4054</v>
+        <v>1.479</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.219</v>
+        <v>32.303</v>
       </c>
       <c r="E17" t="n">
         <v>29.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9762</v>
+        <v>0.9132</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1494,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1076</v>
+        <v>0.1013</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0741</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6445</v>
+        <v>0.6413</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -940,10 +940,10 @@
         <v>0.1326</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8048</v>
+        <v>0.8081</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         <v>0.1663</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1003</v>
+        <v>0.1006</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9034</v>
+        <v>0.9059</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         <v>0.1714</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0668</v>
+        <v>0.067</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5685</v>
+        <v>0.5702</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>0.1013</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1105</v>
+        <v>0.1107</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.622</v>
+        <v>4.921</v>
       </c>
       <c r="E23" t="n">
-        <v>6.32</v>
+        <v>4.7</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.11</v>
@@ -1857,10 +1857,10 @@
         <v>0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0757</v>
+        <v>0.1055</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2164</v>
+        <v>0.1087</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.2042</v>
+        <v>0.1003</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6407</v>
+        <v>0.6437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6048</v>
+        <v>0.6081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5609</v>
+        <v>0.5645</v>
       </c>
     </row>
     <row r="3">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8226</v>
+        <v>0.8255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8048</v>
+        <v>0.8081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7831</v>
+        <v>0.7867</v>
       </c>
     </row>
     <row r="4">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1105</v>
+        <v>0.1108</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0044</v>
+        <v>1.0073</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0048</v>
+        <v>1.0081</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0053</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -547,10 +547,10 @@
         <v>10.579</v>
       </c>
       <c r="E2" t="n">
-        <v>6.39</v>
+        <v>8.52</v>
       </c>
       <c r="F2" t="n">
-        <v>0.604</v>
+        <v>0.8054</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,7 +559,7 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0704</v>
+        <v>0.0905</v>
       </c>
       <c r="J2" t="n">
         <v>0.1481</v>
@@ -610,10 +610,10 @@
         <v>32.785</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6</v>
+        <v>30.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8724</v>
+        <v>0.9273</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,7 +622,7 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="J3" t="n">
         <v>0.1216</v>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.407</v>
+        <v>25.118</v>
       </c>
       <c r="E5" t="n">
-        <v>0.39</v>
+        <v>25.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9583</v>
+        <v>1.0271</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1058</v>
+        <v>0.1127</v>
       </c>
       <c r="J5" t="n">
-        <v>0.12</v>
+        <v>0.1234</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0997</v>
+        <v>1.1342</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1258</v>
+        <v>0.1119</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1576</v>
+        <v>1.0185</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>flips (cheap/fair)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.118</v>
+        <v>0.407</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9993</v>
+        <v>1.3087</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,33 +811,33 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1099</v>
+        <v>0.1409</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1234</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1342</v>
+        <v>1.0997</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1119</v>
+        <v>0.1258</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0185</v>
+        <v>1.1576</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>flips (cheap/fair)</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -862,10 +862,10 @@
         <v>84.60299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>77.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9113</v>
+        <v>1.0425</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -874,7 +874,7 @@
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1011</v>
+        <v>0.1143</v>
       </c>
       <c r="J7" t="n">
         <v>0.0689</v>
@@ -925,10 +925,10 @@
         <v>15.005</v>
       </c>
       <c r="E8" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2262</v>
+        <v>1.2929</v>
       </c>
       <c r="G8" t="n">
         <v>0.11</v>
@@ -937,7 +937,7 @@
         <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1326</v>
+        <v>0.1393</v>
       </c>
       <c r="J8" t="n">
         <v>0.09080000000000001</v>
@@ -988,10 +988,10 @@
         <v>25.337</v>
       </c>
       <c r="E9" t="n">
-        <v>39.6</v>
+        <v>43.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5629</v>
+        <v>1.7287</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,7 +1000,7 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1663</v>
+        <v>0.1829</v>
       </c>
       <c r="J9" t="n">
         <v>0.1006</v>
@@ -1051,10 +1051,10 @@
         <v>39.537</v>
       </c>
       <c r="E10" t="n">
-        <v>63.8</v>
+        <v>66.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6137</v>
+        <v>1.6769</v>
       </c>
       <c r="G10" t="n">
         <v>0.11</v>
@@ -1063,7 +1063,7 @@
         <v>0.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1714</v>
+        <v>0.1777</v>
       </c>
       <c r="J10" t="n">
         <v>0.067</v>
@@ -1114,10 +1114,10 @@
         <v>2.845</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2495</v>
+        <v>2.3901</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,7 +1126,7 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.235</v>
+        <v>0.249</v>
       </c>
       <c r="J11" t="n">
         <v>0.1291</v>
@@ -1177,10 +1177,10 @@
         <v>54.638</v>
       </c>
       <c r="E12" t="n">
-        <v>93.2</v>
+        <v>99.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7058</v>
+        <v>1.8174</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
@@ -1189,7 +1189,7 @@
         <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1806</v>
+        <v>0.1917</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         <v>27.222</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1388</v>
+        <v>1.1498</v>
       </c>
       <c r="G13" t="n">
         <v>0.11</v>
@@ -1250,7 +1250,7 @@
         <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1225</v>
+        <v>0.1235</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         <v>76.22</v>
       </c>
       <c r="E15" t="n">
-        <v>76.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0024</v>
+        <v>1.0155</v>
       </c>
       <c r="G15" t="n">
         <v>0.11</v>
@@ -1372,7 +1372,7 @@
         <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1102</v>
+        <v>0.1115</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         <v>5.565</v>
       </c>
       <c r="E16" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3658</v>
+        <v>1.4916</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1433,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1466</v>
+        <v>0.1592</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>32.303</v>
       </c>
       <c r="E17" t="n">
-        <v>29.5</v>
+        <v>31.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9132</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.11</v>
@@ -1494,7 +1494,7 @@
         <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1013</v>
+        <v>0.1084</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>17.373</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9785</v>
+        <v>1.0188</v>
       </c>
       <c r="G18" t="n">
         <v>0.11</v>
@@ -1555,7 +1555,7 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1079</v>
+        <v>0.1119</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>15.482</v>
       </c>
       <c r="E20" t="n">
-        <v>14.14</v>
+        <v>16.06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9133</v>
+        <v>1.0373</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1677,7 +1677,7 @@
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1013</v>
+        <v>0.1137</v>
       </c>
       <c r="J20" t="n">
         <v>0.1107</v>
@@ -1726,10 +1726,10 @@
         <v>2.05</v>
       </c>
       <c r="E21" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2437</v>
+        <v>1.4144</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
@@ -1738,7 +1738,7 @@
         <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1331</v>
+        <v>0.1494</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>16.457</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4</v>
+        <v>18.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.112</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1097</v>
+        <v>0.1212</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         <v>35.691</v>
       </c>
       <c r="E25" t="n">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
       <c r="F25" t="n">
-        <v>1.244</v>
+        <v>1.3813</v>
       </c>
       <c r="G25" t="n">
         <v>0.11</v>
@@ -1979,7 +1979,7 @@
         <v>0.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1344</v>
+        <v>0.1481</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         <v>15.804</v>
       </c>
       <c r="E26" t="n">
-        <v>21.77</v>
+        <v>24.18</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3775</v>
+        <v>1.53</v>
       </c>
       <c r="G26" t="n">
         <v>0.11</v>
@@ -2040,7 +2040,7 @@
         <v>0.01</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1478</v>
+        <v>0.163</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.579</v>
+        <v>10.654</v>
       </c>
       <c r="E2" t="n">
         <v>8.52</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8054</v>
+        <v>0.7997</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0905</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1481</v>
+        <v>0.147</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3809</v>
+        <v>1.3705</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0992</v>
+        <v>0.0985</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8919</v>
+        <v>0.8849</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.785</v>
+        <v>32.877</v>
       </c>
       <c r="E3" t="n">
         <v>30.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9273</v>
+        <v>0.9246</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,24 +622,24 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.1126</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0.1027</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.1216</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.116</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>cheap</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0.103</v>
-      </c>
       <c r="N3" t="n">
-        <v>0.93</v>
+        <v>0.9271</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.133</v>
+        <v>32.202</v>
       </c>
       <c r="E4" t="n">
         <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5357</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6828</v>
+        <v>0.6812</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.0654</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5536</v>
+        <v>0.5522</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.457</v>
+        <v>16.505</v>
       </c>
       <c r="E24" t="n">
         <v>18.3</v>
       </c>
       <c r="F24" t="n">
-        <v>1.112</v>
+        <v>1.1088</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1212</v>
+        <v>0.1209</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0697</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5972</v>
+        <v>0.5951</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1216</v>
+        <v>0.1213</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1016</v>
+        <v>0.1013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9237</v>
+        <v>0.9205</v>
       </c>
       <c r="E5" t="n">
-        <v>0.916</v>
+        <v>0.9126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9067</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1216</v>
+        <v>0.1213</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1216</v>
+        <v>0.1213</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1055</v>
+        <v>1.1024</v>
       </c>
       <c r="E6" t="n">
-        <v>1.116</v>
+        <v>1.1126</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1289</v>
+        <v>1.1251</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1216</v>
+        <v>0.1213</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1416</v>
+        <v>0.1413</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2873</v>
+        <v>1.2842</v>
       </c>
       <c r="E7" t="n">
-        <v>1.316</v>
+        <v>1.3126</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3511</v>
+        <v>1.3473</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.05</v>
+        <v>2.104</v>
       </c>
       <c r="E21" t="n">
         <v>2.9</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4144</v>
+        <v>1.3784</v>
       </c>
       <c r="G21" t="n">
         <v>0.11</v>
@@ -1738,7 +1738,7 @@
         <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1494</v>
+        <v>0.1459</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4932</v>
+        <v>0.4604</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -880,7 +880,7 @@
         <v>0.0689</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.5894</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.337</v>
+        <v>26.044</v>
       </c>
       <c r="E9" t="n">
         <v>43.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7287</v>
+        <v>1.6818</v>
       </c>
       <c r="G9" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1829</v>
+        <v>0.1782</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1006</v>
+        <v>0.095</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9059</v>
+        <v>0.8505</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7692</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         <v>0.1777</v>
       </c>
       <c r="J10" t="n">
-        <v>0.067</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5702</v>
+        <v>0.5705</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.845</v>
+        <v>2.763</v>
       </c>
       <c r="E11" t="n">
         <v>6.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3901</v>
+        <v>2.4608</v>
       </c>
       <c r="G11" t="n">
         <v>0.11</v>
@@ -1126,13 +1126,13 @@
         <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.249</v>
+        <v>0.2561</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1291</v>
+        <v>0.133</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1905</v>
+        <v>1.2298</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.0965</v>
+        <v>0.0994</v>
       </c>
       <c r="N11" t="n">
-        <v>0.865</v>
+        <v>0.8935</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.565</v>
+        <v>4.636</v>
       </c>
       <c r="E16" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4916</v>
+        <v>1.7904</v>
       </c>
       <c r="G16" t="n">
         <v>0.11</v>
@@ -1433,7 +1433,7 @@
         <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1592</v>
+        <v>0.189</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.1318</v>
+        <v>0.1369</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2175</v>
+        <v>1.2685</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.804</v>
+        <v>15.834</v>
       </c>
       <c r="E26" t="n">
         <v>24.18</v>
       </c>
       <c r="F26" t="n">
-        <v>1.53</v>
+        <v>1.5271</v>
       </c>
       <c r="G26" t="n">
         <v>0.11</v>
@@ -2040,7 +2040,7 @@
         <v>0.01</v>
       </c>
       <c r="I26" t="n">
-        <v>0.163</v>
+        <v>0.1627</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.132</v>
+        <v>0.1317</v>
       </c>
       <c r="N26" t="n">
-        <v>1.2198</v>
+        <v>1.2173</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -940,10 +940,10 @@
         <v>0.1393</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8081</v>
+        <v>0.8068</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         <v>0.1782</v>
       </c>
       <c r="J9" t="n">
-        <v>0.095</v>
+        <v>0.0949</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8505</v>
+        <v>0.8495</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         <v>0.1777</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5705</v>
+        <v>0.5698</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.482</v>
+        <v>17.315</v>
       </c>
       <c r="E20" t="n">
         <v>16.06</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0373</v>
+        <v>0.9275</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
@@ -1677,10 +1677,10 @@
         <v>0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1137</v>
+        <v>0.1027</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1107</v>
+        <v>0.1144</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.1075</v>
+        <v>0.1109</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>0.1055</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1087</v>
+        <v>0.1085</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0708</v>
+        <v>0.0707</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6437</v>
+        <v>0.6425</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6081</v>
+        <v>0.6068</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5645</v>
+        <v>0.5631</v>
       </c>
     </row>
     <row r="3">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8255</v>
+        <v>0.8244</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8081</v>
+        <v>0.8068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7867</v>
+        <v>0.7853</v>
       </c>
     </row>
     <row r="4">
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1108</v>
+        <v>0.1107</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0073</v>
+        <v>1.0062</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0081</v>
+        <v>1.0068</v>
       </c>
       <c r="F4" t="n">
-        <v>1.009</v>
+        <v>1.0075</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/justified_pnav.xlsx
+++ b/outputs/justified_pnav.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.654</v>
+        <v>10.719</v>
       </c>
       <c r="E2" t="n">
         <v>8.52</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7997</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.11</v>
@@ -559,13 +559,13 @@
         <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09</v>
+        <v>0.0895</v>
       </c>
       <c r="J2" t="n">
-        <v>0.147</v>
+        <v>0.1462</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3705</v>
+        <v>1.3617</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0985</v>
+        <v>0.0979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8849</v>
+        <v>0.879</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.877</v>
+        <v>33.268</v>
       </c>
       <c r="E3" t="n">
         <v>30.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9246</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.11</v>
@@ -622,13 +622,13 @@
         <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1025</v>
+        <v>0.1014</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1213</v>
+        <v>0.1198</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1126</v>
+        <v>1.0984</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1027</v>
+        <v>0.1015</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9271</v>
+        <v>0.915</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.202</v>
+        <v>32.601</v>
       </c>
       <c r="E4" t="n">
         <v>17.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5357</v>
+        <v>0.5291</v>
       </c>
       <c r="G4" t="n">
         <v>0.11</v>
@@ -685,13 +685,13 @@
         <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0636</v>
+        <v>0.0629</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0781</v>
+        <v>0.0772</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6812</v>
+        <v>0.6716</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0644</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5522</v>
+        <v>0.5442</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.118</v>
+        <v>25.373</v>
       </c>
       <c r="E5" t="n">
         <v>25.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0271</v>
+        <v>1.0168</v>
       </c>
       <c r="G5" t="n">
         <v>0.11</v>
@@ -748,13 +748,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1127</v>
+        <v>0.1117</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1234</v>
+        <v>0.1222</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1342</v>
+        <v>1.1218</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1119</v>
+        <v>0.1107</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0185</v>
+        <v>1.0073</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.407</v>
+        <v>0.411</v>
       </c>
       <c r="E6" t="n">
         <v>0.53</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3087</v>
+        <v>1.2962</v>
       </c>
       <c r="G6" t="n">
         <v>0.11</v>
@@ -811,13 +811,13 @@
         <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1409</v>
+        <v>0.1396</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>0.1188</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0997</v>
+        <v>1.0882</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1258</v>
+        <v>0.1246</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1576</v>
+        <v>1.1455</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.505</v>
+        <v>16.539</v>
       </c>
       <c r="E24" t="n">
         <v>18.3</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1088</v>
+        <v>1.1064</v>
       </c>
       <c r="G24" t="n">
         <v>0.11</v>
@@ -1918,7 +1918,7 @@
         <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1209</v>
+        <v>0.1206</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0694</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5951</v>
+        <v>0.5937</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1213</v>
+        <v>0.1198</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1013</v>
+        <v>0.0998</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9205</v>
+        <v>0.9076</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9126</v>
+        <v>0.8984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9029</v>
+        <v>0.8871</v>
       </c>
     </row>
     <row r="6">
@@ -2218,19 +2218,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1213</v>
+        <v>0.1198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1213</v>
+        <v>0.1198</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1024</v>
+        <v>1.0894</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1126</v>
+        <v>1.0984</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1251</v>
+        <v>1.1093</v>
       </c>
     </row>
     <row r="7">
@@ -2240,19 +2240,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1213</v>
+        <v>0.1198</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1413</v>
+        <v>0.1398</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2842</v>
+        <v>1.2712</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3126</v>
+        <v>1.2984</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3473</v>
+        <v>1.3315</v>
       </c>
     </row>
   </sheetData>
